--- a/Bearing_Stiffness_Study.xlsx
+++ b/Bearing_Stiffness_Study.xlsx
@@ -20,9 +20,11 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="c_A" vbProcedure="false">Step1_Cantilever!$B$5</definedName>
+    <definedName function="false" hidden="false" name="c_b12" vbProcedure="false">Step1_Cantilever!$B$17</definedName>
+    <definedName function="false" hidden="false" name="c_b22" vbProcedure="false">Step1_Cantilever!$B$18</definedName>
     <definedName function="false" hidden="false" name="c_cb" vbProcedure="false">Step1_Cantilever!$B$16</definedName>
-    <definedName function="false" hidden="false" name="c_cba" vbProcedure="false">Step1_Cantilever!$B$17</definedName>
-    <definedName function="false" hidden="false" name="c_cbt" vbProcedure="false">Step1_Cantilever!$B$18</definedName>
+    <definedName function="false" hidden="false" name="c_cba" vbProcedure="false">Step1_Cantilever!$B$19</definedName>
+    <definedName function="false" hidden="false" name="c_cbt" vbProcedure="false">Step1_Cantilever!$B$20</definedName>
     <definedName function="false" hidden="false" name="c_G" vbProcedure="false">Step1_Cantilever!$B$8</definedName>
     <definedName function="false" hidden="false" name="c_I" vbProcedure="false">Step1_Cantilever!$B$6</definedName>
     <definedName function="false" hidden="false" name="c_J" vbProcedure="false">Step1_Cantilever!$B$7</definedName>
@@ -32,34 +34,35 @@
     <definedName function="false" hidden="false" name="c_mb" vbProcedure="false">Step1_Cantilever!$B$10</definedName>
     <definedName function="false" hidden="false" name="c_mlat" vbProcedure="false">Step1_Cantilever!$B$12</definedName>
     <definedName function="false" hidden="false" name="c_rho" vbProcedure="false">Step1_Cantilever!$B$9</definedName>
-    <definedName function="false" hidden="false" name="in_alpha" vbProcedure="false">Inputs!$C$33</definedName>
-    <definedName function="false" hidden="false" name="in_ap" vbProcedure="false">Inputs!$C$27</definedName>
-    <definedName function="false" hidden="false" name="in_arr" vbProcedure="false">Inputs!$C$35</definedName>
-    <definedName function="false" hidden="false" name="in_bp" vbProcedure="false">Inputs!$C$28</definedName>
-    <definedName function="false" hidden="false" name="in_chr" vbProcedure="false">Inputs!$C$39</definedName>
-    <definedName function="false" hidden="false" name="in_chth" vbProcedure="false">Inputs!$C$38</definedName>
+    <definedName function="false" hidden="false" name="in_alpha" vbProcedure="false">Inputs!$C$34</definedName>
+    <definedName function="false" hidden="false" name="in_ap" vbProcedure="false">Inputs!$C$28</definedName>
+    <definedName function="false" hidden="false" name="in_arr" vbProcedure="false">Inputs!$C$36</definedName>
+    <definedName function="false" hidden="false" name="in_bp" vbProcedure="false">Inputs!$C$29</definedName>
+    <definedName function="false" hidden="false" name="in_chr" vbProcedure="false">Inputs!$C$40</definedName>
+    <definedName function="false" hidden="false" name="in_chth" vbProcedure="false">Inputs!$C$39</definedName>
     <definedName function="false" hidden="false" name="in_Db" vbProcedure="false">Inputs!$C$12</definedName>
     <definedName function="false" hidden="false" name="in_Dib" vbProcedure="false">Inputs!$C$13</definedName>
-    <definedName function="false" hidden="false" name="in_dm" vbProcedure="false">Inputs!$C$34</definedName>
+    <definedName function="false" hidden="false" name="in_dm" vbProcedure="false">Inputs!$C$35</definedName>
     <definedName function="false" hidden="false" name="in_Eb" vbProcedure="false">Inputs!$C$9</definedName>
-    <definedName function="false" hidden="false" name="in_Ep" vbProcedure="false">Inputs!$C$24</definedName>
+    <definedName function="false" hidden="false" name="in_Ep" vbProcedure="false">Inputs!$C$25</definedName>
     <definedName function="false" hidden="false" name="in_freq" vbProcedure="false">Inputs!$C$5</definedName>
     <definedName function="false" hidden="false" name="in_g" vbProcedure="false">Inputs!$C$6</definedName>
+    <definedName function="false" hidden="false" name="in_Icg" vbProcedure="false">Inputs!$C$18</definedName>
     <definedName function="false" hidden="false" name="in_Jm" vbProcedure="false">Inputs!$C$17</definedName>
-    <definedName function="false" hidden="false" name="in_Ka" vbProcedure="false">Inputs!$C$19</definedName>
-    <definedName function="false" hidden="false" name="in_ka1" vbProcedure="false">Inputs!$C$30</definedName>
-    <definedName function="false" hidden="false" name="in_Kr" vbProcedure="false">Inputs!$C$20</definedName>
-    <definedName function="false" hidden="false" name="in_kr1" vbProcedure="false">Inputs!$C$31</definedName>
-    <definedName function="false" hidden="false" name="in_Kt" vbProcedure="false">Inputs!$C$22</definedName>
-    <definedName function="false" hidden="false" name="in_Kth" vbProcedure="false">Inputs!$C$21</definedName>
-    <definedName function="false" hidden="false" name="in_kth1" vbProcedure="false">Inputs!$C$32</definedName>
+    <definedName function="false" hidden="false" name="in_Ka" vbProcedure="false">Inputs!$C$20</definedName>
+    <definedName function="false" hidden="false" name="in_ka1" vbProcedure="false">Inputs!$C$31</definedName>
+    <definedName function="false" hidden="false" name="in_Kr" vbProcedure="false">Inputs!$C$21</definedName>
+    <definedName function="false" hidden="false" name="in_kr1" vbProcedure="false">Inputs!$C$32</definedName>
+    <definedName function="false" hidden="false" name="in_Kt" vbProcedure="false">Inputs!$C$23</definedName>
+    <definedName function="false" hidden="false" name="in_Kth" vbProcedure="false">Inputs!$C$22</definedName>
+    <definedName function="false" hidden="false" name="in_kth1" vbProcedure="false">Inputs!$C$33</definedName>
     <definedName function="false" hidden="false" name="in_Lb" vbProcedure="false">Inputs!$C$14</definedName>
     <definedName function="false" hidden="false" name="in_nub" vbProcedure="false">Inputs!$C$10</definedName>
-    <definedName function="false" hidden="false" name="in_nup" vbProcedure="false">Inputs!$C$25</definedName>
-    <definedName function="false" hidden="false" name="in_s0" vbProcedure="false">Inputs!$C$36</definedName>
-    <definedName function="false" hidden="false" name="in_smax" vbProcedure="false">Inputs!$C$37</definedName>
+    <definedName function="false" hidden="false" name="in_nup" vbProcedure="false">Inputs!$C$26</definedName>
+    <definedName function="false" hidden="false" name="in_s0" vbProcedure="false">Inputs!$C$37</definedName>
+    <definedName function="false" hidden="false" name="in_smax" vbProcedure="false">Inputs!$C$38</definedName>
     <definedName function="false" hidden="false" name="in_tol" vbProcedure="false">Inputs!$C$7</definedName>
-    <definedName function="false" hidden="false" name="in_tp" vbProcedure="false">Inputs!$C$26</definedName>
+    <definedName function="false" hidden="false" name="in_tp" vbProcedure="false">Inputs!$C$27</definedName>
     <definedName function="false" hidden="false" name="in_wb" vbProcedure="false">Inputs!$C$11</definedName>
     <definedName function="false" hidden="false" name="in_Wm" vbProcedure="false">Inputs!$C$16</definedName>
     <definedName function="false" hidden="false" name="p_beta" vbProcedure="false">Step3_Plate!$B$7</definedName>
@@ -71,41 +74,50 @@
     <definedName function="false" hidden="false" name="q_cb" vbProcedure="false">Step4_SpacedPair!$B$8</definedName>
     <definedName function="false" hidden="false" name="q_cs" vbProcedure="false">Step4_SpacedPair!$B$19</definedName>
     <definedName function="false" hidden="false" name="q_det" vbProcedure="false">Step4_SpacedPair!$B$18</definedName>
+    <definedName function="false" hidden="false" name="q_f11" vbProcedure="false">Step4_SpacedPair!$B$20</definedName>
+    <definedName function="false" hidden="false" name="q_f12" vbProcedure="false">Step4_SpacedPair!$B$21</definedName>
+    <definedName function="false" hidden="false" name="q_f22" vbProcedure="false">Step4_SpacedPair!$B$22</definedName>
     <definedName function="false" hidden="false" name="q_K11" vbProcedure="false">Step4_SpacedPair!$B$15</definedName>
     <definedName function="false" hidden="false" name="q_K12" vbProcedure="false">Step4_SpacedPair!$B$16</definedName>
     <definedName function="false" hidden="false" name="q_K22" vbProcedure="false">Step4_SpacedPair!$B$17</definedName>
     <definedName function="false" hidden="false" name="q_L" vbProcedure="false">Step4_SpacedPair!$B$7</definedName>
     <definedName function="false" hidden="false" name="q_off" vbProcedure="false">Step4_SpacedPair!$B$5</definedName>
     <definedName function="false" hidden="false" name="q_slc0" vbProcedure="false">Step4_SpacedPair!$B$6</definedName>
-    <definedName function="false" hidden="false" name="s1_fax" vbProcedure="false">Step1_Cantilever!$B$24</definedName>
-    <definedName function="false" hidden="false" name="s1_flat" vbProcedure="false">Step1_Cantilever!$B$23</definedName>
-    <definedName function="false" hidden="false" name="s1_ftor" vbProcedure="false">Step1_Cantilever!$B$25</definedName>
-    <definedName function="false" hidden="false" name="s1_kax" vbProcedure="false">Step1_Cantilever!$B$21</definedName>
-    <definedName function="false" hidden="false" name="s1_klat" vbProcedure="false">Step1_Cantilever!$B$20</definedName>
-    <definedName function="false" hidden="false" name="s1_ktor" vbProcedure="false">Step1_Cantilever!$B$22</definedName>
+    <definedName function="false" hidden="false" name="s1_fax" vbProcedure="false">Step1_Cantilever!$B$26</definedName>
+    <definedName function="false" hidden="false" name="s1_flat" vbProcedure="false">Step1_Cantilever!$B$25</definedName>
+    <definedName function="false" hidden="false" name="s1_ftor" vbProcedure="false">Step1_Cantilever!$B$27</definedName>
+    <definedName function="false" hidden="false" name="s1_kax" vbProcedure="false">Step1_Cantilever!$B$23</definedName>
+    <definedName function="false" hidden="false" name="s1_klat" vbProcedure="false">Step1_Cantilever!$B$22</definedName>
+    <definedName function="false" hidden="false" name="s1_ktor" vbProcedure="false">Step1_Cantilever!$B$24</definedName>
     <definedName function="false" hidden="false" name="s2_c1" vbProcedure="false">Step2_CBUSH!$B$5</definedName>
     <definedName function="false" hidden="false" name="s2_c2" vbProcedure="false">Step2_CBUSH!$B$6</definedName>
     <definedName function="false" hidden="false" name="s2_c3" vbProcedure="false">Step2_CBUSH!$B$7</definedName>
     <definedName function="false" hidden="false" name="s2_ct" vbProcedure="false">Step2_CBUSH!$B$8</definedName>
-    <definedName function="false" hidden="false" name="s2_fax" vbProcedure="false">Step2_CBUSH!$B$17</definedName>
-    <definedName function="false" hidden="false" name="s2_flat" vbProcedure="false">Step2_CBUSH!$B$16</definedName>
-    <definedName function="false" hidden="false" name="s2_ftor" vbProcedure="false">Step2_CBUSH!$B$18</definedName>
-    <definedName function="false" hidden="false" name="s2_kax" vbProcedure="false">Step2_CBUSH!$B$14</definedName>
-    <definedName function="false" hidden="false" name="s2_klat" vbProcedure="false">Step2_CBUSH!$B$13</definedName>
-    <definedName function="false" hidden="false" name="s2_ktor" vbProcedure="false">Step2_CBUSH!$B$15</definedName>
+    <definedName function="false" hidden="false" name="s2_f12" vbProcedure="false">Step2_CBUSH!$B$9</definedName>
+    <definedName function="false" hidden="false" name="s2_f22" vbProcedure="false">Step2_CBUSH!$B$10</definedName>
+    <definedName function="false" hidden="false" name="s2_fax" vbProcedure="false">Step2_CBUSH!$B$19</definedName>
+    <definedName function="false" hidden="false" name="s2_flat" vbProcedure="false">Step2_CBUSH!$B$18</definedName>
+    <definedName function="false" hidden="false" name="s2_ftor" vbProcedure="false">Step2_CBUSH!$B$20</definedName>
+    <definedName function="false" hidden="false" name="s2_Ipiv" vbProcedure="false">Step2_CBUSH!$B$23</definedName>
+    <definedName function="false" hidden="false" name="s2_kax" vbProcedure="false">Step2_CBUSH!$B$16</definedName>
+    <definedName function="false" hidden="false" name="s2_klat" vbProcedure="false">Step2_CBUSH!$B$15</definedName>
+    <definedName function="false" hidden="false" name="s2_Kreq" vbProcedure="false">Step2_CBUSH!$B$25</definedName>
+    <definedName function="false" hidden="false" name="s2_ktor" vbProcedure="false">Step2_CBUSH!$B$17</definedName>
     <definedName function="false" hidden="false" name="s3_c1" vbProcedure="false">Step3_Plate!$B$14</definedName>
     <definedName function="false" hidden="false" name="s3_c2" vbProcedure="false">Step3_Plate!$B$15</definedName>
     <definedName function="false" hidden="false" name="s3_c3" vbProcedure="false">Step3_Plate!$B$16</definedName>
     <definedName function="false" hidden="false" name="s3_c4" vbProcedure="false">Step3_Plate!$B$17</definedName>
     <definedName function="false" hidden="false" name="s3_ct" vbProcedure="false">Step3_Plate!$B$18</definedName>
-    <definedName function="false" hidden="false" name="s3_fax" vbProcedure="false">Step3_Plate!$B$28</definedName>
-    <definedName function="false" hidden="false" name="s3_flat" vbProcedure="false">Step3_Plate!$B$27</definedName>
-    <definedName function="false" hidden="false" name="s3_ftor" vbProcedure="false">Step3_Plate!$B$29</definedName>
-    <definedName function="false" hidden="false" name="s3_kax" vbProcedure="false">Step3_Plate!$B$25</definedName>
-    <definedName function="false" hidden="false" name="s3_klat" vbProcedure="false">Step3_Plate!$B$24</definedName>
-    <definedName function="false" hidden="false" name="s3_ktor" vbProcedure="false">Step3_Plate!$B$26</definedName>
-    <definedName function="false" hidden="false" name="s4_flat" vbProcedure="false">Step4_SpacedPair!$B$21</definedName>
-    <definedName function="false" hidden="false" name="s4_klat" vbProcedure="false">Step4_SpacedPair!$B$20</definedName>
+    <definedName function="false" hidden="false" name="s3_f12" vbProcedure="false">Step3_Plate!$B$19</definedName>
+    <definedName function="false" hidden="false" name="s3_f22" vbProcedure="false">Step3_Plate!$B$20</definedName>
+    <definedName function="false" hidden="false" name="s3_fax" vbProcedure="false">Step3_Plate!$B$30</definedName>
+    <definedName function="false" hidden="false" name="s3_flat" vbProcedure="false">Step3_Plate!$B$29</definedName>
+    <definedName function="false" hidden="false" name="s3_ftor" vbProcedure="false">Step3_Plate!$B$31</definedName>
+    <definedName function="false" hidden="false" name="s3_kax" vbProcedure="false">Step3_Plate!$B$27</definedName>
+    <definedName function="false" hidden="false" name="s3_klat" vbProcedure="false">Step3_Plate!$B$26</definedName>
+    <definedName function="false" hidden="false" name="s3_ktor" vbProcedure="false">Step3_Plate!$B$28</definedName>
+    <definedName function="false" hidden="false" name="s4_flat" vbProcedure="false">Step4_SpacedPair!$B$24</definedName>
+    <definedName function="false" hidden="false" name="s4_klat" vbProcedure="false">Step4_SpacedPair!$B$23</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -117,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="377">
   <si>
     <t xml:space="preserve">Bearing stiffness modeling study: hand calcs vs FEM</t>
   </si>
@@ -167,7 +179,7 @@
     <t xml:space="preserve">FEM SETUP NOTES (to keep FEM apples-to-apples with the hand calcs)</t>
   </si>
   <si>
-    <t xml:space="preserve">• Beam as CBAR, ≥10 elements. Tip mass as CONM2 with no offset; give it only the polar inertia Jm (no rocking inertia) unless you add it to the hand calc.</t>
+    <t xml:space="preserve">• Beam as CBAR, ≥10 elements, PBAR shear factors K1/K2 blank. Payload as CONM2 at the CG node, no offset: polar inertia Jm about the beam axis, rocking inertia Icg about BOTH transverse axes, products 0.</t>
   </si>
   <si>
     <t xml:space="preserve">• Steps 1-2: base node SPC 123456 (step 1) / CBUSH to grounded coincident node (step 2). Don't give the CBUSH a length.</t>
@@ -188,7 +200,7 @@
     <t xml:space="preserve">HAND-CALC ASSUMPTIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">• Lateral: Rayleigh, tip point mass + 33/140 of beam mass. With a soft root the true beam-mass fraction approaches 1/3, so hand calc runs slightly high when the beam mass is not small vs M.</t>
+    <t xml:space="preserve">• Lateral: 2-DOF tip (translation with M + 33/140 beam mass, rocking with payload Icg about its CG), using the tip flexibility matrix [f11 f12; f12 f22]. Beam rotary inertia neglected. Lowest root: λ = [tr + √(tr² − 4det)]/2 of F·M, f = 1/(2π√λ). Icg = 0 recovers the point-mass result.</t>
   </si>
   <si>
     <t xml:space="preserve">• Axial: tip mass + 1/3 beam mass. Torsion: Jm + 1/3 beam polar mass inertia.</t>
@@ -317,96 +329,117 @@
     <t xml:space="preserve">in</t>
   </si>
   <si>
+    <t xml:space="preserve">Test fixture: sized so beam stays &lt;~15% of lateral compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beam ID (0 = solid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_Dib</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tube keeps beam mass small vs payload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arm length: bearing (pair center) to mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_Lb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given: pair center to payload CG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tip mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payload weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_Wm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lbf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payload polar mass inertia about beam (spin) axis, through CG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_Jm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slinch·in²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLACEHOLDER: 500 lbf solid cylinder 16 in dia × 12 in long, mr²/2. Torsion mode only. CAD lbm·in² ÷ 386.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payload transverse (rocking) mass inertia about CG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_Icg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLACEHOLDER: same cylinder, m(3r²+h²)/12. Feeds lateral mode. 0 = point mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bearing PAIR as one CBUSH (ORBIS 6x6 diagonal, about pair center)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pair axial stiffness Ka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_Ka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lbf/in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLACEHOLDER (100 mm bore DB pair class): replace with ORBIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pair radial stiffness Kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_Kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLACEHOLDER: replace with ORBIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pair tilt stiffness Kθ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_Kth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lbf·in/rad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spin-axis restraint Kt (motor/brake, NOT bearing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_Kt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLACEHOLDER: bearings carry ~0 torque about spin axis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plate / housing wall (Step 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plate modulus E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_Ep</t>
+  </si>
+  <si>
     <t xml:space="preserve">PLACEHOLDER</t>
   </si>
   <si>
-    <t xml:space="preserve">Beam ID (0 = solid)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in_Dib</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arm length: bearing (pair center) to mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in_Lb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steps 1-3: base/CBUSH point to tip mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tip mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tip weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in_Wm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lbf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tip polar mass inertia about beam axis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in_Jm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slinch·in²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLACEHOLDER: 5 lbf, 4 in dia disk ≈ mr²/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bearing PAIR as one CBUSH (ORBIS 6x6 diagonal, about pair center)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pair axial stiffness Ka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in_Ka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lbf/in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLACEHOLDER: replace with ORBIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pair radial stiffness Kr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in_Kr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pair tilt stiffness Kθ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in_Kth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lbf·in/rad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spin-axis restraint Kt (motor/brake, NOT bearing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in_Kt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLACEHOLDER: bearings carry ~0 torque about spin axis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plate / housing wall (Step 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plate modulus E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in_Ep</t>
-  </si>
-  <si>
     <t xml:space="preserve">Plate Poisson ratio</t>
   </si>
   <si>
@@ -431,6 +464,9 @@
     <t xml:space="preserve">in_bp</t>
   </si>
   <si>
+    <t xml:space="preserve">PLACEHOLDER: 150 mm OD bearing (7020 class)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Single bearing (Step 4, spaced pair)</t>
   </si>
   <si>
@@ -716,66 +752,84 @@
     <t xml:space="preserve">Beam-only compliances</t>
   </si>
   <si>
-    <t xml:space="preserve">Lateral beam compliance</t>
+    <t xml:space="preserve">Lateral beam compliance f11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L³/3EI (tip force → tip deflection)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beam coupling f12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/lbf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L²/2EI (tip force → tip rotation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beam rotation f22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L/EI (tip moment → tip rotation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axial beam compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L/EA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torsion beam compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L/GJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 1 results (rigid base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lateral stiffness at mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3EI/L³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axial stiffness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torsional stiffness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GJ/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First lateral mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-DOF tip (translation m_eff + rocking Icg); = (1/2π)√(k/m) when Icg = 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First axial mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First torsion mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 2: CBUSH (pair diagonal) at the beam base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lateral compliance chain (series)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beam bending</t>
   </si>
   <si>
     <t xml:space="preserve">L³/3EI</t>
   </si>
   <si>
-    <t xml:space="preserve">Axial beam compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L/EA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torsion beam compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L/GJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Step 1 results (rigid base)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lateral stiffness at mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3EI/L³</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axial stiffness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA/L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torsional stiffness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GJ/L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First lateral mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1/2π)√(k/m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First axial mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First torsion mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Step 2: CBUSH (pair diagonal) at the beam base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lateral compliance chain (series)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beam bending</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bearing radial</t>
   </si>
   <si>
@@ -788,7 +842,19 @@
     <t xml:space="preserve">L²/Kθ</t>
   </si>
   <si>
-    <t xml:space="preserve">Total lateral compliance</t>
+    <t xml:space="preserve">Total lateral compliance f11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coupling f12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L²/2EI + L/Kθ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotation f22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L/EI + 1/Kθ</t>
   </si>
   <si>
     <t xml:space="preserve">  share: beam</t>
@@ -818,7 +884,7 @@
     <t xml:space="preserve">1/(L/GJ + 1/Kt)</t>
   </si>
   <si>
-    <t xml:space="preserve">Beam-mass fraction kept at 33/140 (slightly unconservative with soft root)</t>
+    <t xml:space="preserve">2-DOF tip; beam-mass fraction kept at 33/140 (slightly unconservative with soft root)</t>
   </si>
   <si>
     <t xml:space="preserve">Lateral mode drop vs Step 1</t>
@@ -827,6 +893,42 @@
     <t xml:space="preserve">What the bearing alone costs you</t>
   </si>
   <si>
+    <t xml:space="preserve">What it takes (rigid arm, rigid radial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rocking inertia about pair center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icg + m·L²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rigid-body rocking estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1/2π)√(Kθ/I_pivot): ceiling from the bearing tilt alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tilt stiffness needed to hit requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2πf_req)²·I_pivot, before any beam/radial/housing compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  vs current pair Kθ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple of today's tilt stiffness needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load-center span that gives it (kr·s²/2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-bearing kr from Inputs; the real arm will need more</t>
+  </si>
+  <si>
     <t xml:space="preserve">Step 3: CBUSH into a clamped annular plate (housing wall)</t>
   </si>
   <si>
@@ -896,7 +998,7 @@
     <t xml:space="preserve">Step 3a results (rigid hub = RBE2 at bore)</t>
   </si>
   <si>
-    <t xml:space="preserve">Massless plate: set plate density 0 in FEM</t>
+    <t xml:space="preserve">2-DOF tip. Massless plate: set plate density 0 in FEM</t>
   </si>
   <si>
     <t xml:space="preserve">Lateral mode drop vs Step 2</t>
@@ -992,6 +1094,18 @@
     <t xml:space="preserve">[1 L]·K⁻¹·[1 L]ᵀ + housing</t>
   </si>
   <si>
+    <t xml:space="preserve">Tip f11 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overhang beam + support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tip f12 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tip f22 total</t>
+  </si>
+  <si>
     <t xml:space="preserve">Runs a bit above Step 2: shaft between load centers is rigid here and the flexible overhang is shorter. FEM must model it the same way.</t>
   </si>
   <si>
@@ -1032,6 +1146,12 @@
   </si>
   <si>
     <t xml:space="preserve">Tilt share of compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tip f12 (1/lbf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tip f22 (rad/lbf·in)</t>
   </si>
   <si>
     <t xml:space="preserve">Note: 'Tilt share' = support (bearing + housing) share of total lateral compliance. Once it's small, more span buys nothing; the overhang beam or housing is the limit.</t>
@@ -1352,7 +1472,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1450,6 +1570,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1717,52 +1841,52 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.47</c:v>
+                  <c:v>0.945</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.705333333333333</c:v>
+                  <c:v>2.21533333333333</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.940666666666667</c:v>
+                  <c:v>3.48566666666667</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.176</c:v>
+                  <c:v>4.756</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.41133333333333</c:v>
+                  <c:v>6.02633333333333</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.64666666666667</c:v>
+                  <c:v>7.29666666666667</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.882</c:v>
+                  <c:v>8.567</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.11733333333333</c:v>
+                  <c:v>9.83733333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.35266666666667</c:v>
+                  <c:v>11.1076666666667</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.588</c:v>
+                  <c:v>12.378</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.82333333333333</c:v>
+                  <c:v>13.6483333333333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.05866666666667</c:v>
+                  <c:v>14.9186666666667</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.294</c:v>
+                  <c:v>16.189</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.52933333333333</c:v>
+                  <c:v>17.4593333333333</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.76466666666667</c:v>
+                  <c:v>18.7296666666667</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1774,52 +1898,52 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>88.1569212584955</c:v>
+                  <c:v>16.6549044966351</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>97.5674241296759</c:v>
+                  <c:v>23.3215494089985</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>104.048580708267</c:v>
+                  <c:v>28.2121510773847</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.617669913722</c:v>
+                  <c:v>31.747041518866</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>111.926887919012</c:v>
+                  <c:v>34.3167819115056</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>114.387617947817</c:v>
+                  <c:v>36.2142225493623</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>116.26220186631</c:v>
+                  <c:v>37.6425318644204</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>117.721488191762</c:v>
+                  <c:v>38.739273573162</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>118.879452083477</c:v>
+                  <c:v>39.597569688643</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>119.813986537241</c:v>
+                  <c:v>40.2811484871143</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>120.579562232179</c:v>
+                  <c:v>40.8343155760539</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>121.215091257173</c:v>
+                  <c:v>41.2884177369269</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>121.74891990558</c:v>
+                  <c:v>41.6660293419021</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>122.202069174392</c:v>
+                  <c:v>41.9836880004565</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>122.590383026267</c:v>
+                  <c:v>42.2537064812791</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>122.925981359936</c:v>
+                  <c:v>42.485391516071</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1887,52 +2011,52 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.47</c:v>
+                  <c:v>0.945</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.705333333333333</c:v>
+                  <c:v>2.21533333333333</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.940666666666667</c:v>
+                  <c:v>3.48566666666667</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.176</c:v>
+                  <c:v>4.756</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.41133333333333</c:v>
+                  <c:v>6.02633333333333</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.64666666666667</c:v>
+                  <c:v>7.29666666666667</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.882</c:v>
+                  <c:v>8.567</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.11733333333333</c:v>
+                  <c:v>9.83733333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.35266666666667</c:v>
+                  <c:v>11.1076666666667</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.588</c:v>
+                  <c:v>12.378</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.82333333333333</c:v>
+                  <c:v>13.6483333333333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.05866666666667</c:v>
+                  <c:v>14.9186666666667</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.294</c:v>
+                  <c:v>16.189</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.52933333333333</c:v>
+                  <c:v>17.4593333333333</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.76466666666667</c:v>
+                  <c:v>18.7296666666667</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2057,52 +2181,52 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.47</c:v>
+                  <c:v>0.945</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.705333333333333</c:v>
+                  <c:v>2.21533333333333</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.940666666666667</c:v>
+                  <c:v>3.48566666666667</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.176</c:v>
+                  <c:v>4.756</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.41133333333333</c:v>
+                  <c:v>6.02633333333333</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.64666666666667</c:v>
+                  <c:v>7.29666666666667</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.882</c:v>
+                  <c:v>8.567</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.11733333333333</c:v>
+                  <c:v>9.83733333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.35266666666667</c:v>
+                  <c:v>11.1076666666667</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.588</c:v>
+                  <c:v>12.378</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.82333333333333</c:v>
+                  <c:v>13.6483333333333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.05866666666667</c:v>
+                  <c:v>14.9186666666667</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.294</c:v>
+                  <c:v>16.189</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.52933333333333</c:v>
+                  <c:v>17.4593333333333</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.76466666666667</c:v>
+                  <c:v>18.7296666666667</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2118,11 +2242,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="63873569"/>
-        <c:axId val="1380443"/>
+        <c:axId val="27411553"/>
+        <c:axId val="82833574"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="63873569"/>
+        <c:axId val="27411553"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2198,12 +2322,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1380443"/>
+        <c:crossAx val="82833574"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1380443"/>
+        <c:axId val="82833574"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2279,7 +2403,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63873569"/>
+        <c:crossAx val="27411553"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2711,7 +2835,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1"/>
       <c r="B29" s="3" t="s">
         <v>23</v>
@@ -2791,7 +2915,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -2960,7 +3084,7 @@
         <v>64</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>65</v>
@@ -2977,33 +3101,35 @@
         <v>68</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -3012,384 +3138,401 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>0.0259</v>
+        <v>41.44</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="E18" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>84</v>
-      </c>
+      <c r="A19" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>1500000</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B21" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="13" t="n">
-        <v>280000</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>50000</v>
+        <v>7700000</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="A23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="A24" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="11" t="n">
-        <v>0.33</v>
+        <v>101</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>10000000</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>66</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>0.925</v>
+        <v>12</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="A29" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>2.953</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30" s="13" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="A30" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>750000</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>5000</v>
+        <v>3000000</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>15</v>
+        <v>119</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>20000</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1.42</v>
+        <v>15</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1</v>
+        <v>4.92</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>0.47</v>
+        <v>1</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4</v>
+        <v>0.945</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>0</v>
+        <v>134</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C39" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3418,7 +3561,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3436,7 +3579,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -3446,21 +3589,21 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="1"/>
@@ -3473,7 +3616,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="1"/>
@@ -3486,7 +3629,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="1"/>
@@ -3496,7 +3639,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="1"/>
@@ -3506,7 +3649,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="1"/>
@@ -3516,7 +3659,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="1"/>
@@ -3526,7 +3669,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">SUM(B5:B10)</f>
@@ -3550,7 +3693,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -3560,27 +3703,27 @@
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="17" t="str">
@@ -3599,7 +3742,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="17" t="str">
@@ -3618,7 +3761,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="17" t="str">
@@ -3637,7 +3780,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="17" t="str">
@@ -3656,7 +3799,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="17" t="str">
@@ -3678,7 +3821,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="17" t="str">
@@ -3708,7 +3851,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B22" s="19" t="str">
         <f aca="false">IF(OR(B16="",B17=""),"",LN(B17/B16)/LN(4))</f>
@@ -3732,7 +3875,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -3742,25 +3885,25 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -3776,7 +3919,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -3789,7 +3932,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -3802,7 +3945,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -3829,7 +3972,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -3839,7 +3982,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3853,7 +3996,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>36</v>
@@ -3862,12 +4005,12 @@
         <v>37</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -3875,52 +4018,52 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">PI()*(in_Db^2-in_Dib^2)/4</f>
-        <v>0.785398163397448</v>
+        <v>8.63937979737193</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">PI()*(in_Db^4-in_Dib^4)/64</f>
-        <v>0.0490873852123405</v>
+        <v>32.9376354774805</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="false">2*c_I</f>
-        <v>0.098174770424681</v>
+        <v>65.875270954961</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">in_Eb/(2*(1+in_nub))</f>
@@ -3930,102 +4073,102 @@
         <v>55</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">in_wb/in_g</f>
         <v>0.000253826827941672</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">c_rho*c_A*in_Lb</f>
-        <v>0.00119613074691833</v>
+        <v>0.0460510337563559</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">in_Wm/in_g</f>
-        <v>0.012950348364371</v>
+        <v>1.2950348364371</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B12" s="22" t="n">
         <f aca="false">c_M+33/140*c_mb</f>
-        <v>0.0132322934690018</v>
+        <v>1.30588972296538</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B13" s="22" t="n">
         <f aca="false">c_M+c_mb/3</f>
-        <v>0.0133490586133438</v>
+        <v>1.31038518102255</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B14" s="22" t="n">
         <f aca="false">in_Jm+c_rho*c_J*in_Lb/3</f>
-        <v>0.0259498387811216</v>
+        <v>41.5570463774641</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -4033,142 +4176,172 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">in_Lb^3/(3*in_Eb*c_I)</f>
-        <v>0.000146677195553491</v>
+        <v>9.37225746550807E-006</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B17" s="22" t="n">
-        <f aca="false">in_Lb/(in_Eb*c_A)</f>
-        <v>7.63943726841098E-007</v>
+        <f aca="false">in_Lb^2/(2*in_Eb*c_I)</f>
+        <v>6.69446961822005E-007</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>134</v>
+        <v>210</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B18" s="22" t="n">
-        <f aca="false">in_Lb/(c_G*c_J)</f>
-        <v>1.62567225071786E-005</v>
+        <f aca="false">in_Lb/(in_Eb*c_I)</f>
+        <v>6.37568535068576E-008</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
+      <c r="A19" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="22" t="n">
+        <f aca="false">in_Lb/(in_Eb*c_A)</f>
+        <v>2.43073003994895E-007</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B20" s="23" t="n">
-        <f aca="false">1/c_cb</f>
-        <v>6817.69239060285</v>
+        <v>216</v>
+      </c>
+      <c r="B20" s="22" t="n">
+        <f aca="false">in_Lb/(c_G*c_J)</f>
+        <v>8.47966151641207E-008</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B21" s="23" t="n">
-        <f aca="false">1/c_cba</f>
-        <v>1308996.93899575</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>209</v>
-      </c>
+      <c r="A21" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B22" s="23" t="n">
+        <f aca="false">1/c_cb</f>
+        <v>106697.879745645</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B23" s="23" t="n">
+        <f aca="false">1/c_cba</f>
+        <v>4113990.37970092</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B24" s="23" t="n">
         <f aca="false">1/c_cbt</f>
-        <v>61513.014050552</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B23" s="24" t="n">
-        <f aca="false">SQRT(s1_klat/c_mlat)/(2*PI())</f>
-        <v>114.240809201571</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B24" s="24" t="n">
-        <f aca="false">SQRT(s1_kax/c_max)/(2*PI())</f>
-        <v>1576.02871914394</v>
+        <v>11792923.5508344</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="10"/>
+        <v>95</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B25" s="24" t="n">
-        <f aca="false">SQRT(s1_ktor/c_Jeff)/(2*PI())</f>
-        <v>245.03961604488</v>
+        <f aca="false">1/SQRT((((c_cb)*c_mlat+(c_b22)*in_Icg)+SQRT(((c_cb)*c_mlat+(c_b22)*in_Icg)^2-4*c_mlat*in_Icg*((c_cb)*(c_b22)-(c_b12)^2)))/2)/(2*PI())</f>
+        <v>42.4641223713926</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="10"/>
+      <c r="D25" s="10" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <f aca="false">SQRT(s1_kax/c_max)/(2*PI())</f>
+        <v>282.002060124489</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <f aca="false">SQRT(s1_ktor/c_Jeff)/(2*PI())</f>
+        <v>84.7829525558879</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4186,7 +4359,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -4196,7 +4369,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4210,7 +4383,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>36</v>
@@ -4219,12 +4392,12 @@
         <v>37</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -4232,204 +4405,317 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B5" s="22" t="n">
         <f aca="false">c_cb</f>
-        <v>0.000146677195553491</v>
+        <v>9.37225746550807E-006</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">1/in_Kr</f>
-        <v>6.66666666666667E-007</v>
+        <v>1.66666666666667E-007</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="false">in_Lb^2/in_Kth</f>
-        <v>0.000128571428571429</v>
+        <v>5.72727272727273E-005</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">s2_c1+s2_c2+s2_c3</f>
-        <v>0.000275915290791586</v>
+        <v>6.6811651404902E-005</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="17" t="n">
-        <f aca="false">s2_c1/s2_ct</f>
-        <v>0.531602272323081</v>
-      </c>
-      <c r="C9" s="1"/>
+        <v>238</v>
+      </c>
+      <c r="B9" s="22" t="n">
+        <f aca="false">c_b12+in_Lb/in_Kth</f>
+        <v>3.39671968909473E-006</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="D9" s="10" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B10" s="17" t="n">
-        <f aca="false">s2_c2/s2_ct</f>
-        <v>0.0024162005112295</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="10"/>
+        <v>240</v>
+      </c>
+      <c r="B10" s="22" t="n">
+        <f aca="false">c_b22+1/in_Kth</f>
+        <v>1.93626983376988E-007</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B11" s="17" t="n">
-        <f aca="false">s2_c3/s2_ct</f>
-        <v>0.46598152716569</v>
+        <f aca="false">s2_c1/s2_ct</f>
+        <v>0.14027878773283</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="10" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
+      <c r="A12" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">s2_c2/s2_ct</f>
+        <v>0.00249457487073038</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13" s="23" t="n">
-        <f aca="false">1/s2_ct</f>
-        <v>3624.30076684425</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>83</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="B13" s="17" t="n">
+        <f aca="false">s2_c3/s2_ct</f>
+        <v>0.85722663739644</v>
+      </c>
+      <c r="C13" s="1"/>
       <c r="D13" s="10" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B14" s="23" t="n">
-        <f aca="false">1/(c_cba+1/in_Ka)</f>
-        <v>306377.831142272</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>231</v>
-      </c>
+      <c r="A14" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B15" s="23" t="n">
+        <f aca="false">1/s2_ct</f>
+        <v>14967.4492243823</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B16" s="23" t="n">
+        <f aca="false">1/(c_cba+1/in_Ka)</f>
+        <v>1099215.5583067</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="23" t="n">
         <f aca="false">1/(c_cbt+1/in_Kt)</f>
-        <v>27581.0920251274</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B16" s="24" t="n">
-        <f aca="false">SQRT(s2_klat/c_mlat)/(2*PI())</f>
-        <v>83.2941853559316</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B17" s="24" t="n">
-        <f aca="false">SQRT(s2_kax/c_max)/(2*PI())</f>
-        <v>762.471263539485</v>
+        <v>1709996.21760696</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="10"/>
+        <v>95</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B18" s="24" t="n">
-        <f aca="false">SQRT(s2_ktor/c_Jeff)/(2*PI())</f>
-        <v>164.081088436435</v>
+        <f aca="false">1/SQRT((((s2_ct)*c_mlat+(s2_f22)*in_Icg)+SQRT(((s2_ct)*c_mlat+(s2_f22)*in_Icg)^2-4*c_mlat*in_Icg*((s2_ct)*(s2_f22)-(s2_f12)^2)))/2)/(2*PI())</f>
+        <v>16.453991975958</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="10"/>
+      <c r="D18" s="10" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B19" s="17" t="n">
+      <c r="A19" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <f aca="false">SQRT(s2_kax/c_max)/(2*PI())</f>
+        <v>145.76796085664</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <f aca="false">SQRT(s2_ktor/c_Jeff)/(2*PI())</f>
+        <v>32.2845970331995</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B21" s="17" t="n">
         <f aca="false">s2_flat/s1_flat-1</f>
-        <v>-0.270889396371798</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="10" t="s">
-        <v>235</v>
+        <v>-0.612520145075628</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B23" s="22" t="n">
+        <f aca="false">in_Icg+c_mlat*in_Lb^2</f>
+        <v>612.157367827734</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <f aca="false">SQRT(in_Kth/s2_Ipiv)/(2*PI())</f>
+        <v>17.8498246346273</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B25" s="23" t="n">
+        <f aca="false">(2*PI()*in_freq)^2*s2_Ipiv</f>
+        <v>543757594.65047</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B26" s="25" t="n">
+        <f aca="false">s2_Kreq/in_Kth</f>
+        <v>70.6178694351259</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B27" s="21" t="n">
+        <f aca="false">SQRT(2*s2_Kreq/in_kr1)</f>
+        <v>19.0395657277238</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4448,7 +4734,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -4458,7 +4744,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4472,7 +4758,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>36</v>
@@ -4481,12 +4767,12 @@
         <v>37</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -4494,22 +4780,22 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">in_Ep*in_tp^3/(12*(1-in_nup^2))</f>
-        <v>14612.0899263083</v>
+        <v>935173.755283732</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">in_Ep/(2*(1+in_nup))</f>
@@ -4522,37 +4808,37 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="false">in_bp/in_ap</f>
-        <v>0.23125</v>
+        <v>0.246083333333333</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="B8" s="21" t="n">
         <f aca="false">in_tp/in_ap</f>
-        <v>0.0625</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -4560,52 +4846,52 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="B10" s="23" t="n">
         <f aca="false">16*PI()*p_D*(1-p_beta^2)/(in_ap^2*((1-p_beta^2)^2-4*p_beta^2*LN(p_beta)^2))</f>
-        <v>99364.6855647225</v>
+        <v>754653.181814772</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="B11" s="23" t="n">
         <f aca="false">4*PI()*p_D*(1+p_beta^2)/((1+p_beta^2)*LN(1/p_beta)-(1-p_beta^2))</f>
-        <v>324544.83752709</v>
+        <v>22762182.1047333</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">4*PI()*p_G*in_tp/(1/in_bp^2-1/in_ap^2)</f>
-        <v>10676289.1946082</v>
+        <v>438515238.495727</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -4613,236 +4899,262 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B14" s="22" t="n">
         <f aca="false">c_cb</f>
-        <v>0.000146677195553491</v>
+        <v>9.37225746550807E-006</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B15" s="22" t="n">
         <f aca="false">1/in_Kr</f>
-        <v>6.66666666666667E-007</v>
+        <v>1.66666666666667E-007</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">in_Lb^2/in_Kth</f>
-        <v>0.000128571428571429</v>
+        <v>5.72727272727273E-005</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">in_Lb^2/p_Kth</f>
-        <v>0.000110924580635164</v>
+        <v>1.93742409216688E-005</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">s3_c1+s3_c2+s3_c3+s3_c4</f>
-        <v>0.00038683987142675</v>
+        <v>8.61858923265708E-005</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B19" s="17" t="n">
-        <f aca="false">s3_c1/s3_ct</f>
-        <v>0.379167729046422</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>238</v>
+      </c>
+      <c r="B19" s="22" t="n">
+        <f aca="false">s2_f12+in_Lb/p_Kth</f>
+        <v>4.31930259012658E-006</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="D19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B20" s="17" t="n">
-        <f aca="false">s3_c2/s3_ct</f>
-        <v>0.0017233659607213</v>
-      </c>
-      <c r="C20" s="1"/>
+        <v>240</v>
+      </c>
+      <c r="B20" s="22" t="n">
+        <f aca="false">s2_f22+1/p_Kth</f>
+        <v>2.37559502473742E-007</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="D20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B21" s="17" t="n">
-        <f aca="false">s3_c3/s3_ct</f>
-        <v>0.332363435281966</v>
+        <f aca="false">s3_c1/s3_ct</f>
+        <v>0.108744682134232</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B22" s="17" t="n">
-        <f aca="false">s3_c4/s3_ct</f>
-        <v>0.286745469710891</v>
+        <f aca="false">s3_c2/s3_ct</f>
+        <v>0.00193380450288944</v>
       </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="10" t="s">
-        <v>257</v>
-      </c>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
+      <c r="A23" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" s="17" t="n">
+        <f aca="false">s3_c3/s3_ct</f>
+        <v>0.664525547356552</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B24" s="23" t="n">
-        <f aca="false">1/s3_ct</f>
-        <v>2585.04894108195</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="10"/>
+        <v>286</v>
+      </c>
+      <c r="B24" s="17" t="n">
+        <f aca="false">s3_c4/s3_ct</f>
+        <v>0.224795966006327</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="10" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B25" s="23" t="n">
-        <f aca="false">1/(c_cba+1/in_Ka+1/p_Ka)</f>
-        <v>75030.6798078002</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="10"/>
+      <c r="A25" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B26" s="23" t="n">
+        <f aca="false">1/s3_ct</f>
+        <v>11602.8270173366</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B27" s="23" t="n">
+        <f aca="false">1/(c_cba+1/in_Ka+1/p_Ka)</f>
+        <v>447456.98582851</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B28" s="23" t="n">
         <f aca="false">1/(c_cbt+1/in_Kt+1/p_Kt)</f>
-        <v>27510.0227187057</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="10"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B27" s="24" t="n">
-        <f aca="false">SQRT(s3_klat/c_mlat)/(2*PI())</f>
-        <v>70.3456026207545</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B28" s="24" t="n">
-        <f aca="false">SQRT(s3_kax/c_max)/(2*PI())</f>
-        <v>377.323845867506</v>
+        <v>1703353.96533777</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B29" s="24" t="n">
-        <f aca="false">SQRT(s3_ktor/c_Jeff)/(2*PI())</f>
-        <v>163.869554919922</v>
+        <f aca="false">1/SQRT((((s3_ct)*c_mlat+(s3_f22)*in_Icg)+SQRT(((s3_ct)*c_mlat+(s3_f22)*in_Icg)^2-4*c_mlat*in_Icg*((s3_ct)*(s3_f22)-(s3_f12)^2)))/2)/(2*PI())</f>
+        <v>14.5017165499889</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="10"/>
+      <c r="D29" s="10" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B30" s="17" t="n">
-        <f aca="false">s3_flat/s2_flat-1</f>
-        <v>-0.155456022288295</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="10" t="s">
-        <v>261</v>
-      </c>
+      <c r="A30" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <f aca="false">SQRT(s3_kax/c_max)/(2*PI())</f>
+        <v>93.0028573102841</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
+      <c r="A31" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B31" s="24" t="n">
+        <f aca="false">SQRT(s3_ktor/c_Jeff)/(2*PI())</f>
+        <v>32.2218334187576</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B32" s="21"/>
+        <v>290</v>
+      </c>
+      <c r="B32" s="17" t="n">
+        <f aca="false">s3_flat/s2_flat-1</f>
+        <v>-0.11865056387664</v>
+      </c>
       <c r="C32" s="1"/>
       <c r="D32" s="10" t="s">
-        <v>264</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="10" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -4861,7 +5173,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -4871,7 +5183,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4885,7 +5197,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>36</v>
@@ -4894,12 +5206,12 @@
         <v>37</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -4907,67 +5219,67 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">in_dm/2*TAN(RADIANS(in_alpha))</f>
-        <v>0.190243926626097</v>
+        <v>0.659155013380562</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="B6" s="21" t="n">
         <f aca="false">in_s0+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>0.850487853252194</v>
+        <v>2.26331002676112</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="false">in_Lb-q_slc0/2</f>
-        <v>5.5747560733739</v>
+        <v>19.8683449866194</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">q_L^3/(3*in_Eb*c_I)</f>
-        <v>0.000117648516310725</v>
+        <v>7.93727456025856E-006</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -4975,22 +5287,22 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="B10" s="23" t="n">
         <f aca="false">2*in_kr1</f>
-        <v>1500000</v>
+        <v>6000000</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">2*in_kr1/in_Kr-1</f>
@@ -4998,40 +5310,40 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="10" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">in_kr1*q_slc0^2/2+2*in_kth1</f>
-        <v>281248.595698572</v>
+        <v>7723858.41585616</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">(in_kr1*q_slc0^2/2+2*in_kth1)/in_Kth-1</f>
-        <v>0.00445927035204363</v>
+        <v>0.00309849556573472</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="10" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -5039,106 +5351,147 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="B15" s="23" t="n">
         <f aca="false">2*in_kr1</f>
-        <v>1500000</v>
+        <v>6000000</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="B16" s="23" t="n">
         <f aca="false">-in_kr1*q_slc0</f>
-        <v>-637865.889939146</v>
+        <v>-6789930.08028337</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="B17" s="23" t="n">
         <f aca="false">in_kr1*q_slc0^2+2*in_kth1</f>
-        <v>552497.191397145</v>
+        <v>15407716.8317123</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">q_K11*q_K22-q_K12^2</f>
-        <v>421872893547.858</v>
+        <v>46343150495136.9</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">(q_K22-2*q_L*q_K12+q_L^2*q_K11)/q_det+in_chr+q_L^2*in_chth</f>
-        <v>0.000128667305783041</v>
+        <v>5.72624828062634E-005</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B20" s="23" t="n">
-        <f aca="false">1/(q_cb+q_cs)</f>
-        <v>4059.82852217803</v>
+        <v>321</v>
+      </c>
+      <c r="B20" s="22" t="n">
+        <f aca="false">q_cb+q_cs</f>
+        <v>6.5199757366522E-005</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="10"/>
+        <v>142</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B21" s="24" t="n">
-        <f aca="false">SQRT(s4_klat/c_mlat)/(2*PI())</f>
-        <v>88.1569212584955</v>
+      <c r="A21" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B21" s="22" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*q_K11-q_K12)/q_det+q_L*in_chth</f>
+        <v>3.31808862871736E-006</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>291</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="1"/>
+        <v>324</v>
+      </c>
+      <c r="B22" s="22" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+q_K11/q_det+in_chth</f>
+        <v>1.89790073730259E-007</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="D22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B23" s="23" t="n">
+        <f aca="false">1/q_f11</f>
+        <v>15337.4803893591</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <f aca="false">1/SQRT((((q_f11)*c_mlat+(q_f22)*in_Icg)+SQRT(((q_f11)*c_mlat+(q_f22)*in_Icg)^2-4*c_mlat*in_Icg*((q_f11)*(q_f22)-(q_f12)^2)))/2)/(2*PI())</f>
+        <v>16.6549044966351</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5156,17 +5509,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5177,10 +5530,12 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5191,6 +5546,8 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
@@ -5203,661 +5560,797 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>304</v>
+        <v>338</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="n">
+      <c r="A5" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*0/15</f>
-        <v>0.47</v>
-      </c>
-      <c r="B5" s="25" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="B5" s="26" t="n">
         <f aca="false">A5+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>0.850487853252194</v>
-      </c>
-      <c r="C5" s="26" t="n">
+        <v>2.26331002676112</v>
+      </c>
+      <c r="C5" s="27" t="n">
         <f aca="false">in_kr1*B5^2+2*in_kth1</f>
-        <v>552497.191397145</v>
-      </c>
-      <c r="D5" s="27" t="n">
+        <v>15407716.8317123</v>
+      </c>
+      <c r="D5" s="28" t="n">
         <f aca="false">(C5-2*q_L*(-in_kr1*B5)+q_L^2*2*in_kr1)/(2*in_kr1*C5-(-in_kr1*B5)^2)+in_chr+q_L^2*in_chth</f>
-        <v>0.000128667305783041</v>
-      </c>
-      <c r="E5" s="26" t="n">
+        <v>5.72624828062634E-005</v>
+      </c>
+      <c r="E5" s="27" t="n">
         <f aca="false">1/(q_cb+D5)</f>
-        <v>4059.82852217803</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <f aca="false">SQRT(E5/c_mlat)/(2*PI())</f>
-        <v>88.1569212584955</v>
-      </c>
-      <c r="G5" s="29" t="n">
+        <v>15337.4803893591</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D5))*c_mlat+(L5)*in_Icg)+SQRT((((q_cb+D5))*c_mlat+(L5)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D5))*(L5)-(K5)^2)))/2)/(2*PI())</f>
+        <v>16.6549044966351</v>
+      </c>
+      <c r="G5" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H5" s="30"/>
-      <c r="I5" s="31" t="str">
+      <c r="H5" s="31"/>
+      <c r="I5" s="32" t="str">
         <f aca="false">IF(H5="","",H5/F5-1)</f>
         <v/>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="32" t="n">
         <f aca="false">D5/(q_cb+D5)</f>
-        <v>0.522367197889792</v>
+        <v>0.878262207087076</v>
+      </c>
+      <c r="K5" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B5))/(2*in_kr1*C5-(-in_kr1*B5)^2)+q_L*in_chth</f>
+        <v>3.31808862871736E-006</v>
+      </c>
+      <c r="L5" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C5-(-in_kr1*B5)^2)+in_chth</f>
+        <v>1.89790073730259E-007</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="n">
+      <c r="A6" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*1/15</f>
-        <v>0.705333333333333</v>
-      </c>
-      <c r="B6" s="25" t="n">
+        <v>2.21533333333333</v>
+      </c>
+      <c r="B6" s="26" t="n">
         <f aca="false">A6+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>1.08582118658553</v>
-      </c>
-      <c r="C6" s="26" t="n">
+        <v>3.53364336009446</v>
+      </c>
+      <c r="C6" s="27" t="n">
         <f aca="false">in_kr1*B6^2+2*in_kth1</f>
-        <v>894255.736928502</v>
-      </c>
-      <c r="D6" s="27" t="n">
+        <v>37499906.1890189</v>
+      </c>
+      <c r="D6" s="28" t="n">
         <f aca="false">(C6-2*q_L*(-in_kr1*B6)+q_L^2*2*in_kr1)/(2*in_kr1*C6-(-in_kr1*B6)^2)+in_chr+q_L^2*in_chth</f>
-        <v>8.34437924642188E-005</v>
-      </c>
-      <c r="E6" s="26" t="n">
+        <v>2.51044187397588E-005</v>
+      </c>
+      <c r="E6" s="27" t="n">
         <f aca="false">1/(q_cb+D6)</f>
-        <v>4972.84061281115</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <f aca="false">SQRT(E6/c_mlat)/(2*PI())</f>
-        <v>97.5674241296759</v>
-      </c>
-      <c r="G6" s="29" t="n">
+        <v>30264.7927550213</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D6))*c_mlat+(L6)*in_Icg)+SQRT((((q_cb+D6))*c_mlat+(L6)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D6))*(L6)-(K6)^2)))/2)/(2*PI())</f>
+        <v>23.3215494089985</v>
+      </c>
+      <c r="G6" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="31" t="str">
+      <c r="H6" s="31"/>
+      <c r="I6" s="32" t="str">
         <f aca="false">IF(H6="","",H6/F6-1)</f>
         <v/>
       </c>
-      <c r="J6" s="31" t="n">
+      <c r="J6" s="32" t="n">
         <f aca="false">D6/(q_cb+D6)</f>
-        <v>0.414952680053052</v>
+        <v>0.759780030394072</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B6))/(2*in_kr1*C6-(-in_kr1*B6)^2)+q_L*in_chth</f>
+        <v>1.75188918795987E-006</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C6-(-in_kr1*B6)^2)+in_chth</f>
+        <v>1.1359774108966E-007</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*2/15</f>
-        <v>0.940666666666667</v>
-      </c>
-      <c r="B7" s="25" t="n">
+        <v>3.48566666666667</v>
+      </c>
+      <c r="B7" s="26" t="n">
         <f aca="false">A7+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>1.32115451991886</v>
-      </c>
-      <c r="C7" s="26" t="n">
+        <v>4.80397669342779</v>
+      </c>
+      <c r="C7" s="27" t="n">
         <f aca="false">in_kr1*B7^2+2*in_kth1</f>
-        <v>1319086.94912653</v>
-      </c>
-      <c r="D7" s="27" t="n">
+        <v>69274576.2129922</v>
+      </c>
+      <c r="D7" s="28" t="n">
         <f aca="false">(C7-2*q_L*(-in_kr1*B7)+q_L^2*2*in_kr1)/(2*in_kr1*C7-(-in_kr1*B7)^2)+in_chr+q_L^2*in_chth</f>
-        <v>5.91720666381723E-005</v>
-      </c>
-      <c r="E7" s="26" t="n">
+        <v>1.44773001257461E-005</v>
+      </c>
+      <c r="E7" s="27" t="n">
         <f aca="false">1/(q_cb+D7)</f>
-        <v>5655.45019319956</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <f aca="false">SQRT(E7/c_mlat)/(2*PI())</f>
-        <v>104.048580708267</v>
-      </c>
-      <c r="G7" s="29" t="n">
+        <v>44613.8289041187</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D7))*c_mlat+(L7)*in_Icg)+SQRT((((q_cb+D7))*c_mlat+(L7)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D7))*(L7)-(K7)^2)))/2)/(2*PI())</f>
+        <v>28.2121510773847</v>
+      </c>
+      <c r="G7" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H7" s="30"/>
-      <c r="I7" s="31" t="str">
+      <c r="H7" s="31"/>
+      <c r="I7" s="32" t="str">
         <f aca="false">IF(H7="","",H7/F7-1)</f>
         <v/>
       </c>
-      <c r="J7" s="31" t="n">
+      <c r="J7" s="32" t="n">
         <f aca="false">D7/(q_cb+D7)</f>
-        <v>0.334644675700869</v>
+        <v>0.645887790803611</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B7))/(2*in_kr1*C7-(-in_kr1*B7)^2)+q_L*in_chth</f>
+        <v>1.24182754526262E-006</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C7-(-in_kr1*B7)^2)+in_chth</f>
+        <v>8.91750627555968E-008</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*3/15</f>
-        <v>1.176</v>
-      </c>
-      <c r="B8" s="25" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="B8" s="26" t="n">
         <f aca="false">A8+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>1.55648785325219</v>
-      </c>
-      <c r="C8" s="26" t="n">
+        <v>6.07431002676112</v>
+      </c>
+      <c r="C8" s="27" t="n">
         <f aca="false">in_kr1*B8^2+2*in_kth1</f>
-        <v>1826990.82799122</v>
-      </c>
-      <c r="D8" s="27" t="n">
+        <v>110731726.903632</v>
+      </c>
+      <c r="D8" s="28" t="n">
         <f aca="false">(C8-2*q_L*(-in_kr1*B8)+q_L^2*2*in_kr1)/(2*in_kr1*C8-(-in_kr1*B8)^2)+in_chr+q_L^2*in_chth</f>
-        <v>4.46087575960319E-005</v>
-      </c>
-      <c r="E8" s="26" t="n">
+        <v>9.6395158298189E-006</v>
+      </c>
+      <c r="E8" s="27" t="n">
         <f aca="false">1/(q_cb+D8)</f>
-        <v>6163.05189852174</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <f aca="false">SQRT(E8/c_mlat)/(2*PI())</f>
-        <v>108.617669913722</v>
-      </c>
-      <c r="G8" s="29" t="n">
+        <v>56893.2084759073</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D8))*c_mlat+(L8)*in_Icg)+SQRT((((q_cb+D8))*c_mlat+(L8)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D8))*(L8)-(K8)^2)))/2)/(2*PI())</f>
+        <v>31.747041518866</v>
+      </c>
+      <c r="G8" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H8" s="30"/>
-      <c r="I8" s="31" t="str">
+      <c r="H8" s="31"/>
+      <c r="I8" s="32" t="str">
         <f aca="false">IF(H8="","",H8/F8-1)</f>
         <v/>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="32" t="n">
         <f aca="false">D8/(q_cb+D8)</f>
-        <v>0.27492608819292</v>
+        <v>0.548422983712695</v>
+      </c>
+      <c r="K8" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B8))/(2*in_kr1*C8-(-in_kr1*B8)^2)+q_L*in_chth</f>
+        <v>1.01280244945841E-006</v>
+      </c>
+      <c r="L8" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C8-(-in_kr1*B8)^2)+in_chth</f>
+        <v>7.83762515831362E-008</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*4/15</f>
-        <v>1.41133333333333</v>
-      </c>
-      <c r="B9" s="25" t="n">
+        <v>6.02633333333333</v>
+      </c>
+      <c r="B9" s="26" t="n">
         <f aca="false">A9+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>1.79182118658553</v>
-      </c>
-      <c r="C9" s="26" t="n">
+        <v>7.34464336009446</v>
+      </c>
+      <c r="C9" s="27" t="n">
         <f aca="false">in_kr1*B9^2+2*in_kth1</f>
-        <v>2417967.37352258</v>
-      </c>
-      <c r="D9" s="27" t="n">
+        <v>161871358.260939</v>
+      </c>
+      <c r="D9" s="28" t="n">
         <f aca="false">(C9-2*q_L*(-in_kr1*B9)+q_L^2*2*in_kr1)/(2*in_kr1*C9-(-in_kr1*B9)^2)+in_chr+q_L^2*in_chth</f>
-        <v>3.5156032189207E-005</v>
-      </c>
-      <c r="E9" s="26" t="n">
+        <v>7.01193055751753E-006</v>
+      </c>
+      <c r="E9" s="27" t="n">
         <f aca="false">1/(q_cb+D9)</f>
-        <v>6544.30780900769</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <f aca="false">SQRT(E9/c_mlat)/(2*PI())</f>
-        <v>111.926887919012</v>
-      </c>
-      <c r="G9" s="29" t="n">
+        <v>66893.1887763652</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D9))*c_mlat+(L9)*in_Icg)+SQRT((((q_cb+D9))*c_mlat+(L9)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D9))*(L9)-(K9)^2)))/2)/(2*PI())</f>
+        <v>34.3167819115056</v>
+      </c>
+      <c r="G9" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H9" s="30"/>
-      <c r="I9" s="31" t="str">
+      <c r="H9" s="31"/>
+      <c r="I9" s="32" t="str">
         <f aca="false">IF(H9="","",H9/F9-1)</f>
         <v/>
       </c>
-      <c r="J9" s="31" t="n">
+      <c r="J9" s="32" t="n">
         <f aca="false">D9/(q_cb+D9)</f>
-        <v>0.230071895989553</v>
+        <v>0.469050394470784</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B9))/(2*in_kr1*C9-(-in_kr1*B9)^2)+q_L*in_chth</f>
+        <v>8.90024864500494E-007</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C9-(-in_kr1*B9)^2)+in_chth</f>
+        <v>7.26735408031474E-008</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*5/15</f>
-        <v>1.64666666666667</v>
-      </c>
-      <c r="B10" s="25" t="n">
+        <v>7.29666666666667</v>
+      </c>
+      <c r="B10" s="26" t="n">
         <f aca="false">A10+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>2.02715451991886</v>
-      </c>
-      <c r="C10" s="26" t="n">
+        <v>8.61497669342779</v>
+      </c>
+      <c r="C10" s="27" t="n">
         <f aca="false">in_kr1*B10^2+2*in_kth1</f>
-        <v>3092016.5857206</v>
-      </c>
-      <c r="D10" s="27" t="n">
+        <v>222693470.284912</v>
+      </c>
+      <c r="D10" s="28" t="n">
         <f aca="false">(C10-2*q_L*(-in_kr1*B10)+q_L^2*2*in_kr1)/(2*in_kr1*C10-(-in_kr1*B10)^2)+in_chr+q_L^2*in_chth</f>
-        <v>2.86524203927563E-005</v>
-      </c>
-      <c r="E10" s="26" t="n">
+        <v>5.41483091080544E-006</v>
+      </c>
+      <c r="E10" s="27" t="n">
         <f aca="false">1/(q_cb+D10)</f>
-        <v>6835.22622980037</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <f aca="false">SQRT(E10/c_mlat)/(2*PI())</f>
-        <v>114.387617947817</v>
-      </c>
-      <c r="G10" s="29" t="n">
+        <v>74894.5551821133</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D10))*c_mlat+(L10)*in_Icg)+SQRT((((q_cb+D10))*c_mlat+(L10)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D10))*(L10)-(K10)^2)))/2)/(2*PI())</f>
+        <v>36.2142225493623</v>
+      </c>
+      <c r="G10" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H10" s="30"/>
-      <c r="I10" s="31" t="str">
+      <c r="H10" s="31"/>
+      <c r="I10" s="32" t="str">
         <f aca="false">IF(H10="","",H10/F10-1)</f>
         <v/>
       </c>
-      <c r="J10" s="31" t="n">
+      <c r="J10" s="32" t="n">
         <f aca="false">D10/(q_cb+D10)</f>
-        <v>0.195845775415835</v>
+        <v>0.405541352451131</v>
+      </c>
+      <c r="K10" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B10))/(2*in_kr1*C10-(-in_kr1*B10)^2)+q_L*in_chth</f>
+        <v>8.16323316260274E-007</v>
+      </c>
+      <c r="L10" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C10-(-in_kr1*B10)^2)+in_chth</f>
+        <v>6.93004448718107E-008</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*6/15</f>
-        <v>1.882</v>
-      </c>
-      <c r="B11" s="25" t="n">
+        <v>8.567</v>
+      </c>
+      <c r="B11" s="26" t="n">
         <f aca="false">A11+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>2.26248785325219</v>
-      </c>
-      <c r="C11" s="26" t="n">
+        <v>9.88531002676112</v>
+      </c>
+      <c r="C11" s="27" t="n">
         <f aca="false">in_kr1*B11^2+2*in_kth1</f>
-        <v>3849138.46458529</v>
-      </c>
-      <c r="D11" s="27" t="n">
+        <v>293198062.975552</v>
+      </c>
+      <c r="D11" s="28" t="n">
         <f aca="false">(C11-2*q_L*(-in_kr1*B11)+q_L^2*2*in_kr1)/(2*in_kr1*C11-(-in_kr1*B11)^2)+in_chr+q_L^2*in_chth</f>
-        <v>2.39726124950875E-005</v>
-      </c>
-      <c r="E11" s="26" t="n">
+        <v>4.3652056609126E-006</v>
+      </c>
+      <c r="E11" s="27" t="n">
         <f aca="false">1/(q_cb+D11)</f>
-        <v>7061.09327352683</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <f aca="false">SQRT(E11/c_mlat)/(2*PI())</f>
-        <v>116.26220186631</v>
-      </c>
-      <c r="G11" s="29" t="n">
+        <v>81284.4224922317</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D11))*c_mlat+(L11)*in_Icg)+SQRT((((q_cb+D11))*c_mlat+(L11)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D11))*(L11)-(K11)^2)))/2)/(2*PI())</f>
+        <v>37.6425318644204</v>
+      </c>
+      <c r="G11" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H11" s="30"/>
-      <c r="I11" s="31" t="str">
+      <c r="H11" s="31"/>
+      <c r="I11" s="32" t="str">
         <f aca="false">IF(H11="","",H11/F11-1)</f>
         <v/>
       </c>
-      <c r="J11" s="31" t="n">
+      <c r="J11" s="32" t="n">
         <f aca="false">D11/(q_cb+D11)</f>
-        <v>0.169272852837928</v>
+        <v>0.354823221207101</v>
+      </c>
+      <c r="K11" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B11))/(2*in_kr1*C11-(-in_kr1*B11)^2)+q_L*in_chth</f>
+        <v>7.68461110661104E-007</v>
+      </c>
+      <c r="L11" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C11-(-in_kr1*B11)^2)+in_chth</f>
+        <v>6.71414998751061E-008</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*7/15</f>
-        <v>2.11733333333333</v>
-      </c>
-      <c r="B12" s="25" t="n">
+        <v>9.83733333333333</v>
+      </c>
+      <c r="B12" s="26" t="n">
         <f aca="false">A12+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>2.49782118658553</v>
-      </c>
-      <c r="C12" s="26" t="n">
+        <v>11.1556433600945</v>
+      </c>
+      <c r="C12" s="27" t="n">
         <f aca="false">in_kr1*B12^2+2*in_kth1</f>
-        <v>4689333.01011665</v>
-      </c>
-      <c r="D12" s="27" t="n">
+        <v>373385136.332859</v>
+      </c>
+      <c r="D12" s="28" t="n">
         <f aca="false">(C12-2*q_L*(-in_kr1*B12)+q_L^2*2*in_kr1)/(2*in_kr1*C12-(-in_kr1*B12)^2)+in_chr+q_L^2*in_chth</f>
-        <v>2.04832775250753E-005</v>
-      </c>
-      <c r="E12" s="26" t="n">
+        <v>3.63460353019163E-006</v>
+      </c>
+      <c r="E12" s="27" t="n">
         <f aca="false">1/(q_cb+D12)</f>
-        <v>7239.46292327686</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <f aca="false">SQRT(E12/c_mlat)/(2*PI())</f>
-        <v>117.721488191762</v>
-      </c>
-      <c r="G12" s="29" t="n">
+        <v>86416.3960407827</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D12))*c_mlat+(L12)*in_Icg)+SQRT((((q_cb+D12))*c_mlat+(L12)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D12))*(L12)-(K12)^2)))/2)/(2*PI())</f>
+        <v>38.739273573162</v>
+      </c>
+      <c r="G12" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H12" s="30"/>
-      <c r="I12" s="31" t="str">
+      <c r="H12" s="31"/>
+      <c r="I12" s="32" t="str">
         <f aca="false">IF(H12="","",H12/F12-1)</f>
         <v/>
       </c>
-      <c r="J12" s="31" t="n">
+      <c r="J12" s="32" t="n">
         <f aca="false">D12/(q_cb+D12)</f>
-        <v>0.148287928189973</v>
+        <v>0.314089338116267</v>
+      </c>
+      <c r="K12" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B12))/(2*in_kr1*C12-(-in_kr1*B12)^2)+q_L*in_chth</f>
+        <v>7.35525478456146E-007</v>
+      </c>
+      <c r="L12" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C12-(-in_kr1*B12)^2)+in_chth</f>
+        <v>6.56769287469616E-008</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="n">
+      <c r="A13" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*8/15</f>
-        <v>2.35266666666667</v>
-      </c>
-      <c r="B13" s="25" t="n">
+        <v>11.1076666666667</v>
+      </c>
+      <c r="B13" s="26" t="n">
         <f aca="false">A13+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>2.73315451991886</v>
-      </c>
-      <c r="C13" s="26" t="n">
+        <v>12.4259766934278</v>
+      </c>
+      <c r="C13" s="27" t="n">
         <f aca="false">in_kr1*B13^2+2*in_kth1</f>
-        <v>5612600.22231468</v>
-      </c>
-      <c r="D13" s="27" t="n">
+        <v>463254690.356832</v>
+      </c>
+      <c r="D13" s="28" t="n">
         <f aca="false">(C13-2*q_L*(-in_kr1*B13)+q_L^2*2*in_kr1)/(2*in_kr1*C13-(-in_kr1*B13)^2)+in_chr+q_L^2*in_chth</f>
-        <v>1.78053948491264E-005</v>
-      </c>
-      <c r="E13" s="26" t="n">
+        <v>3.10318185927776E-006</v>
+      </c>
+      <c r="E13" s="27" t="n">
         <f aca="false">1/(q_cb+D13)</f>
-        <v>7382.58490609314</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <f aca="false">SQRT(E13/c_mlat)/(2*PI())</f>
-        <v>118.879452083477</v>
-      </c>
-      <c r="G13" s="29" t="n">
+        <v>90575.9655217224</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D13))*c_mlat+(L13)*in_Icg)+SQRT((((q_cb+D13))*c_mlat+(L13)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D13))*(L13)-(K13)^2)))/2)/(2*PI())</f>
+        <v>39.597569688643</v>
+      </c>
+      <c r="G13" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H13" s="30"/>
-      <c r="I13" s="31" t="str">
+      <c r="H13" s="31"/>
+      <c r="I13" s="32" t="str">
         <f aca="false">IF(H13="","",H13/F13-1)</f>
         <v/>
       </c>
-      <c r="J13" s="31" t="n">
+      <c r="J13" s="32" t="n">
         <f aca="false">D13/(q_cb+D13)</f>
-        <v>0.131449839260189</v>
+        <v>0.281073693093577</v>
+      </c>
+      <c r="K13" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B13))/(2*in_kr1*C13-(-in_kr1*B13)^2)+q_L*in_chth</f>
+        <v>7.11830926381988E-007</v>
+      </c>
+      <c r="L13" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C13-(-in_kr1*B13)^2)+in_chth</f>
+        <v>6.4638009693887E-008</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="25" t="n">
+      <c r="A14" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*9/15</f>
-        <v>2.588</v>
-      </c>
-      <c r="B14" s="25" t="n">
+        <v>12.378</v>
+      </c>
+      <c r="B14" s="26" t="n">
         <f aca="false">A14+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>2.96848785325219</v>
-      </c>
-      <c r="C14" s="26" t="n">
+        <v>13.6963100267611</v>
+      </c>
+      <c r="C14" s="27" t="n">
         <f aca="false">in_kr1*B14^2+2*in_kth1</f>
-        <v>6618940.10117937</v>
-      </c>
-      <c r="D14" s="27" t="n">
+        <v>562806725.047472</v>
+      </c>
+      <c r="D14" s="28" t="n">
         <f aca="false">(C14-2*q_L*(-in_kr1*B14)+q_L^2*2*in_kr1)/(2*in_kr1*C14-(-in_kr1*B14)^2)+in_chr+q_L^2*in_chth</f>
-        <v>1.57005876976124E-005</v>
-      </c>
-      <c r="E14" s="26" t="n">
+        <v>2.70295706505105E-006</v>
+      </c>
+      <c r="E14" s="27" t="n">
         <f aca="false">1/(q_cb+D14)</f>
-        <v>7499.11300444491</v>
-      </c>
-      <c r="F14" s="28" t="n">
-        <f aca="false">SQRT(E14/c_mlat)/(2*PI())</f>
-        <v>119.813986537241</v>
-      </c>
-      <c r="G14" s="29" t="n">
+        <v>93982.9164640861</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D14))*c_mlat+(L14)*in_Icg)+SQRT((((q_cb+D14))*c_mlat+(L14)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D14))*(L14)-(K14)^2)))/2)/(2*PI())</f>
+        <v>40.2811484871143</v>
+      </c>
+      <c r="G14" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="31" t="str">
+      <c r="H14" s="31"/>
+      <c r="I14" s="32" t="str">
         <f aca="false">IF(H14="","",H14/F14-1)</f>
         <v/>
       </c>
-      <c r="J14" s="31" t="n">
+      <c r="J14" s="32" t="n">
         <f aca="false">D14/(q_cb+D14)</f>
-        <v>0.117740481380593</v>
+        <v>0.254031788050704</v>
+      </c>
+      <c r="K14" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B14))/(2*in_kr1*C14-(-in_kr1*B14)^2)+q_L*in_chth</f>
+        <v>6.94173724110588E-007</v>
+      </c>
+      <c r="L14" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C14-(-in_kr1*B14)^2)+in_chth</f>
+        <v>6.38744681530805E-008</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*10/15</f>
-        <v>2.82333333333333</v>
-      </c>
-      <c r="B15" s="25" t="n">
+        <v>13.6483333333333</v>
+      </c>
+      <c r="B15" s="26" t="n">
         <f aca="false">A15+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>3.20382118658553</v>
-      </c>
-      <c r="C15" s="26" t="n">
+        <v>14.9666433600945</v>
+      </c>
+      <c r="C15" s="27" t="n">
         <f aca="false">in_kr1*B15^2+2*in_kth1</f>
-        <v>7708352.64671072</v>
-      </c>
-      <c r="D15" s="27" t="n">
+        <v>672041240.404779</v>
+      </c>
+      <c r="D15" s="28" t="n">
         <f aca="false">(C15-2*q_L*(-in_kr1*B15)+q_L^2*2*in_kr1)/(2*in_kr1*C15-(-in_kr1*B15)^2)+in_chr+q_L^2*in_chth</f>
-        <v>1.40126607672067E-005</v>
-      </c>
-      <c r="E15" s="26" t="n">
+        <v>2.39292630454578E-006</v>
+      </c>
+      <c r="E15" s="27" t="n">
         <f aca="false">1/(q_cb+D15)</f>
-        <v>7595.25337835988</v>
-      </c>
-      <c r="F15" s="28" t="n">
-        <f aca="false">SQRT(E15/c_mlat)/(2*PI())</f>
-        <v>120.579562232179</v>
-      </c>
-      <c r="G15" s="29" t="n">
+        <v>96803.5387779403</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D15))*c_mlat+(L15)*in_Icg)+SQRT((((q_cb+D15))*c_mlat+(L15)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D15))*(L15)-(K15)^2)))/2)/(2*PI())</f>
+        <v>40.8343155760539</v>
+      </c>
+      <c r="G15" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="31" t="str">
+      <c r="H15" s="31"/>
+      <c r="I15" s="32" t="str">
         <f aca="false">IF(H15="","",H15/F15-1)</f>
         <v/>
       </c>
-      <c r="J15" s="31" t="n">
+      <c r="J15" s="32" t="n">
         <f aca="false">D15/(q_cb+D15)</f>
-        <v>0.106429709031938</v>
+        <v>0.231643734314851</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B15))/(2*in_kr1*C15-(-in_kr1*B15)^2)+q_L*in_chth</f>
+        <v>6.80634170965026E-007</v>
+      </c>
+      <c r="L15" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C15-(-in_kr1*B15)^2)+in_chth</f>
+        <v>6.32969336098918E-008</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*11/15</f>
-        <v>3.05866666666667</v>
-      </c>
-      <c r="B16" s="25" t="n">
+        <v>14.9186666666667</v>
+      </c>
+      <c r="B16" s="26" t="n">
         <f aca="false">A16+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>3.43915451991886</v>
-      </c>
-      <c r="C16" s="26" t="n">
+        <v>16.2369766934278</v>
+      </c>
+      <c r="C16" s="27" t="n">
         <f aca="false">in_kr1*B16^2+2*in_kth1</f>
-        <v>8880837.85890875</v>
-      </c>
-      <c r="D16" s="27" t="n">
+        <v>790958236.428752</v>
+      </c>
+      <c r="D16" s="28" t="n">
         <f aca="false">(C16-2*q_L*(-in_kr1*B16)+q_L^2*2*in_kr1)/(2*in_kr1*C16-(-in_kr1*B16)^2)+in_chr+q_L^2*in_chth</f>
-        <v>1.26356845752462E-005</v>
-      </c>
-      <c r="E16" s="26" t="n">
+        <v>2.14710809865797E-006</v>
+      </c>
+      <c r="E16" s="27" t="n">
         <f aca="false">1/(q_cb+D16)</f>
-        <v>7675.52775547383</v>
-      </c>
-      <c r="F16" s="28" t="n">
-        <f aca="false">SQRT(E16/c_mlat)/(2*PI())</f>
-        <v>121.215091257173</v>
-      </c>
-      <c r="G16" s="29" t="n">
+        <v>99163.2342626157</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D16))*c_mlat+(L16)*in_Icg)+SQRT((((q_cb+D16))*c_mlat+(L16)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D16))*(L16)-(K16)^2)))/2)/(2*PI())</f>
+        <v>41.2884177369269</v>
+      </c>
+      <c r="G16" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H16" s="30"/>
-      <c r="I16" s="31" t="str">
+      <c r="H16" s="31"/>
+      <c r="I16" s="32" t="str">
         <f aca="false">IF(H16="","",H16/F16-1)</f>
         <v/>
       </c>
-      <c r="J16" s="31" t="n">
+      <c r="J16" s="32" t="n">
         <f aca="false">D16/(q_cb+D16)</f>
-        <v>0.0969855476667145</v>
+        <v>0.21291418337438</v>
+      </c>
+      <c r="K16" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B16))/(2*in_kr1*C16-(-in_kr1*B16)^2)+q_L*in_chth</f>
+        <v>6.70003567872049E-007</v>
+      </c>
+      <c r="L16" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C16-(-in_kr1*B16)^2)+in_chth</f>
+        <v>6.28495535357909E-008</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*12/15</f>
-        <v>3.294</v>
-      </c>
-      <c r="B17" s="25" t="n">
+        <v>16.189</v>
+      </c>
+      <c r="B17" s="26" t="n">
         <f aca="false">A17+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>3.67448785325219</v>
-      </c>
-      <c r="C17" s="26" t="n">
+        <v>17.5073100267611</v>
+      </c>
+      <c r="C17" s="27" t="n">
         <f aca="false">in_kr1*B17^2+2*in_kth1</f>
-        <v>10136395.7377734</v>
-      </c>
-      <c r="D17" s="27" t="n">
+        <v>919557713.119392</v>
+      </c>
+      <c r="D17" s="28" t="n">
         <f aca="false">(C17-2*q_L*(-in_kr1*B17)+q_L^2*2*in_kr1)/(2*in_kr1*C17-(-in_kr1*B17)^2)+in_chr+q_L^2*in_chth</f>
-        <v>1.14956832790338E-005</v>
-      </c>
-      <c r="E17" s="26" t="n">
+        <v>1.94835636056794E-006</v>
+      </c>
+      <c r="E17" s="27" t="n">
         <f aca="false">1/(q_cb+D17)</f>
-        <v>7743.28234002466</v>
-      </c>
-      <c r="F17" s="28" t="n">
-        <f aca="false">SQRT(E17/c_mlat)/(2*PI())</f>
-        <v>121.74891990558</v>
-      </c>
-      <c r="G17" s="29" t="n">
+        <v>101156.922406769</v>
+      </c>
+      <c r="F17" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D17))*c_mlat+(L17)*in_Icg)+SQRT((((q_cb+D17))*c_mlat+(L17)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D17))*(L17)-(K17)^2)))/2)/(2*PI())</f>
+        <v>41.6660293419021</v>
+      </c>
+      <c r="G17" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H17" s="30"/>
-      <c r="I17" s="31" t="str">
+      <c r="H17" s="31"/>
+      <c r="I17" s="32" t="str">
         <f aca="false">IF(H17="","",H17/F17-1)</f>
         <v/>
       </c>
-      <c r="J17" s="31" t="n">
+      <c r="J17" s="32" t="n">
         <f aca="false">D17/(q_cb+D17)</f>
-        <v>0.0890143213210595</v>
+        <v>0.197089733186705</v>
+      </c>
+      <c r="K17" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B17))/(2*in_kr1*C17-(-in_kr1*B17)^2)+q_L*in_chth</f>
+        <v>6.61489199747287E-007</v>
+      </c>
+      <c r="L17" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C17-(-in_kr1*B17)^2)+in_chth</f>
+        <v>6.2495966934858E-008</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*13/15</f>
-        <v>3.52933333333333</v>
-      </c>
-      <c r="B18" s="25" t="n">
+        <v>17.4593333333333</v>
+      </c>
+      <c r="B18" s="26" t="n">
         <f aca="false">A18+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>3.90982118658553</v>
-      </c>
-      <c r="C18" s="26" t="n">
+        <v>18.7776433600945</v>
+      </c>
+      <c r="C18" s="27" t="n">
         <f aca="false">in_kr1*B18^2+2*in_kth1</f>
-        <v>11475026.2833048</v>
-      </c>
-      <c r="D18" s="27" t="n">
+        <v>1057839670.4767</v>
+      </c>
+      <c r="D18" s="28" t="n">
         <f aca="false">(C18-2*q_L*(-in_kr1*B18)+q_L^2*2*in_kr1)/(2*in_kr1*C18-(-in_kr1*B18)^2)+in_chr+q_L^2*in_chth</f>
-        <v>1.05396750016196E-005</v>
-      </c>
-      <c r="E18" s="26" t="n">
+        <v>1.7849637665162E-006</v>
+      </c>
+      <c r="E18" s="27" t="n">
         <f aca="false">1/(q_cb+D18)</f>
-        <v>7801.03057670413</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <f aca="false">SQRT(E18/c_mlat)/(2*PI())</f>
-        <v>122.202069174392</v>
-      </c>
-      <c r="G18" s="29" t="n">
+        <v>102856.972477832</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D18))*c_mlat+(L18)*in_Icg)+SQRT((((q_cb+D18))*c_mlat+(L18)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D18))*(L18)-(K18)^2)))/2)/(2*PI())</f>
+        <v>41.9836880004565</v>
+      </c>
+      <c r="G18" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H18" s="30"/>
-      <c r="I18" s="31" t="str">
+      <c r="H18" s="31"/>
+      <c r="I18" s="32" t="str">
         <f aca="false">IF(H18="","",H18/F18-1)</f>
         <v/>
       </c>
-      <c r="J18" s="31" t="n">
+      <c r="J18" s="32" t="n">
         <f aca="false">D18/(q_cb+D18)</f>
-        <v>0.082220326956159</v>
+        <v>0.183595969006485</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B18))/(2*in_kr1*C18-(-in_kr1*B18)^2)+q_L*in_chth</f>
+        <v>6.54553085258823E-007</v>
+      </c>
+      <c r="L18" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C18-(-in_kr1*B18)^2)+in_chth</f>
+        <v>6.22116770811045E-008</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*14/15</f>
-        <v>3.76466666666667</v>
-      </c>
-      <c r="B19" s="25" t="n">
+        <v>18.7296666666667</v>
+      </c>
+      <c r="B19" s="26" t="n">
         <f aca="false">A19+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>4.14515451991886</v>
-      </c>
-      <c r="C19" s="26" t="n">
+        <v>20.0479766934278</v>
+      </c>
+      <c r="C19" s="27" t="n">
         <f aca="false">in_kr1*B19^2+2*in_kth1</f>
-        <v>12896729.4955028</v>
-      </c>
-      <c r="D19" s="27" t="n">
+        <v>1205804108.50067</v>
+      </c>
+      <c r="D19" s="28" t="n">
         <f aca="false">(C19-2*q_L*(-in_kr1*B19)+q_L^2*2*in_kr1)/(2*in_kr1*C19-(-in_kr1*B19)^2)+in_chr+q_L^2*in_chth</f>
-        <v>9.72887055518673E-006</v>
-      </c>
-      <c r="E19" s="26" t="n">
+        <v>1.64870167568975E-006</v>
+      </c>
+      <c r="E19" s="27" t="n">
         <f aca="false">1/(q_cb+D19)</f>
-        <v>7850.68703798018</v>
-      </c>
-      <c r="F19" s="28" t="n">
-        <f aca="false">SQRT(E19/c_mlat)/(2*PI())</f>
-        <v>122.590383026267</v>
-      </c>
-      <c r="G19" s="29" t="n">
+        <v>104319.056858279</v>
+      </c>
+      <c r="F19" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D19))*c_mlat+(L19)*in_Icg)+SQRT((((q_cb+D19))*c_mlat+(L19)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D19))*(L19)-(K19)^2)))/2)/(2*PI())</f>
+        <v>42.2537064812791</v>
+      </c>
+      <c r="G19" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H19" s="30"/>
-      <c r="I19" s="31" t="str">
+      <c r="H19" s="31"/>
+      <c r="I19" s="32" t="str">
         <f aca="false">IF(H19="","",H19/F19-1)</f>
         <v/>
       </c>
-      <c r="J19" s="31" t="n">
+      <c r="J19" s="32" t="n">
         <f aca="false">D19/(q_cb+D19)</f>
-        <v>0.0763783179617915</v>
+        <v>0.171991003848618</v>
+      </c>
+      <c r="K19" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B19))/(2*in_kr1*C19-(-in_kr1*B19)^2)+q_L*in_chth</f>
+        <v>6.48819341969121E-007</v>
+      </c>
+      <c r="L19" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C19-(-in_kr1*B19)^2)+in_chth</f>
+        <v>6.19796920795309E-008</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="26" t="n">
         <f aca="false">in_s0+(in_smax-in_s0)*15/15</f>
-        <v>4</v>
-      </c>
-      <c r="B20" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B20" s="26" t="n">
         <f aca="false">A20+in_arr*in_dm*TAN(RADIANS(in_alpha))</f>
-        <v>4.38048785325219</v>
-      </c>
-      <c r="C20" s="26" t="n">
+        <v>21.3183100267611</v>
+      </c>
+      <c r="C20" s="27" t="n">
         <f aca="false">in_kr1*B20^2+2*in_kth1</f>
-        <v>14401505.3743675</v>
-      </c>
-      <c r="D20" s="27" t="n">
+        <v>1363451027.19131</v>
+      </c>
+      <c r="D20" s="28" t="n">
         <f aca="false">(C20-2*q_L*(-in_kr1*B20)+q_L^2*2*in_kr1)/(2*in_kr1*C20-(-in_kr1*B20)^2)+in_chr+q_L^2*in_chth</f>
-        <v>9.03431785003879E-006</v>
-      </c>
-      <c r="E20" s="26" t="n">
+        <v>1.53364046798269E-006</v>
+      </c>
+      <c r="E20" s="27" t="n">
         <f aca="false">1/(q_cb+D20)</f>
-        <v>7893.72930140617</v>
-      </c>
-      <c r="F20" s="28" t="n">
-        <f aca="false">SQRT(E20/c_mlat)/(2*PI())</f>
-        <v>122.925981359936</v>
-      </c>
-      <c r="G20" s="29" t="n">
+        <v>105586.418737588</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <f aca="false">1/SQRT(((((q_cb+D20))*c_mlat+(L20)*in_Icg)+SQRT((((q_cb+D20))*c_mlat+(L20)*in_Icg)^2-4*c_mlat*in_Icg*(((q_cb+D20))*(L20)-(K20)^2)))/2)/(2*PI())</f>
+        <v>42.485391516071</v>
+      </c>
+      <c r="G20" s="30" t="n">
         <f aca="false">in_freq</f>
         <v>150</v>
       </c>
-      <c r="H20" s="30"/>
-      <c r="I20" s="31" t="str">
+      <c r="H20" s="31"/>
+      <c r="I20" s="32" t="str">
         <f aca="false">IF(H20="","",H20/F20-1)</f>
         <v/>
       </c>
-      <c r="J20" s="31" t="n">
+      <c r="J20" s="32" t="n">
         <f aca="false">D20/(q_cb+D20)</f>
-        <v>0.071314459531068</v>
+        <v>0.161931604645332</v>
+      </c>
+      <c r="K20" s="28" t="n">
+        <f aca="false">q_L^2/(2*in_Eb*c_I)+(q_L*2*in_kr1-(-in_kr1*B20))/(2*in_kr1*C20-(-in_kr1*B20)^2)+q_L*in_chth</f>
+        <v>6.44018680272902E-007</v>
+      </c>
+      <c r="L20" s="28" t="n">
+        <f aca="false">q_L/(in_Eb*c_I)+2*in_kr1/(2*in_kr1*C20-(-in_kr1*B20)^2)+in_chth</f>
+        <v>6.17879258929213E-008</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5871,10 +6364,12 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -5885,6 +6380,8 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5917,7 +6414,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5930,7 +6427,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5954,828 +6451,828 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="D5" s="33" t="n">
+      <c r="A5" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D5" s="34" t="n">
         <f aca="false">s1_klat</f>
-        <v>6817.69239060285</v>
-      </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="31" t="str">
+        <v>106697.879745645</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="32" t="str">
         <f aca="false">IF(E5="","",E5/D5-1)</f>
         <v/>
       </c>
-      <c r="G5" s="32" t="str">
+      <c r="G5" s="33" t="str">
         <f aca="false">IF(E5="","—",IF(ABS(F5)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H5" s="32"/>
-      <c r="I5" s="35" t="s">
-        <v>319</v>
+      <c r="H5" s="33"/>
+      <c r="I5" s="36" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="D6" s="33" t="n">
+      <c r="A6" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="D6" s="34" t="n">
         <f aca="false">s1_kax</f>
-        <v>1308996.93899575</v>
-      </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="31" t="str">
+        <v>4113990.37970092</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="32" t="str">
         <f aca="false">IF(E6="","",E6/D6-1)</f>
         <v/>
       </c>
-      <c r="G6" s="32" t="str">
+      <c r="G6" s="33" t="str">
         <f aca="false">IF(E6="","—",IF(ABS(F6)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="D7" s="33" t="n">
+      <c r="A7" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="D7" s="34" t="n">
         <f aca="false">s1_ktor</f>
-        <v>61513.014050552</v>
-      </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="31" t="str">
+        <v>11792923.5508344</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="32" t="str">
         <f aca="false">IF(E7="","",E7/D7-1)</f>
         <v/>
       </c>
-      <c r="G7" s="32" t="str">
+      <c r="G7" s="33" t="str">
         <f aca="false">IF(E7="","—",IF(ABS(F7)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>322</v>
-      </c>
-      <c r="D8" s="29" t="n">
+      <c r="A8" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="D8" s="30" t="n">
         <f aca="false">s1_flat</f>
-        <v>114.240809201571</v>
-      </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="31" t="str">
+        <v>42.4641223713926</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32" t="str">
         <f aca="false">IF(E8="","",E8/D8-1)</f>
         <v/>
       </c>
-      <c r="G8" s="32" t="str">
+      <c r="G8" s="33" t="str">
         <f aca="false">IF(E8="","—",IF(ABS(F8)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="D9" s="29" t="n">
+      <c r="A9" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>359</v>
+      </c>
+      <c r="D9" s="30" t="n">
         <f aca="false">s1_fax</f>
-        <v>1576.02871914394</v>
-      </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="31" t="str">
+        <v>282.002060124489</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32" t="str">
         <f aca="false">IF(E9="","",E9/D9-1)</f>
         <v/>
       </c>
-      <c r="G9" s="32" t="str">
+      <c r="G9" s="33" t="str">
         <f aca="false">IF(E9="","—",IF(ABS(F9)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="s">
-        <v>316</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>317</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>324</v>
-      </c>
-      <c r="D10" s="37" t="n">
+      <c r="A10" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>353</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="D10" s="38" t="n">
         <f aca="false">s1_ftor</f>
-        <v>245.03961604488</v>
-      </c>
-      <c r="E10" s="38"/>
-      <c r="F10" s="39" t="str">
+        <v>84.7829525558879</v>
+      </c>
+      <c r="E10" s="39"/>
+      <c r="F10" s="40" t="str">
         <f aca="false">IF(E10="","",E10/D10-1)</f>
         <v/>
       </c>
-      <c r="G10" s="36" t="str">
+      <c r="G10" s="37" t="str">
         <f aca="false">IF(E10="","—",IF(ABS(F10)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="D11" s="33" t="n">
+      <c r="A11" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D11" s="34" t="n">
         <f aca="false">s2_klat</f>
-        <v>3624.30076684425</v>
-      </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="31" t="str">
+        <v>14967.4492243823</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="32" t="str">
         <f aca="false">IF(E11="","",E11/D11-1)</f>
         <v/>
       </c>
-      <c r="G11" s="32" t="str">
+      <c r="G11" s="33" t="str">
         <f aca="false">IF(E11="","—",IF(ABS(F11)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H11" s="32"/>
-      <c r="I11" s="35" t="s">
-        <v>327</v>
+      <c r="H11" s="33"/>
+      <c r="I11" s="36" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="B12" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="D12" s="33" t="n">
+      <c r="A12" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="D12" s="34" t="n">
         <f aca="false">s2_kax</f>
-        <v>306377.831142272</v>
-      </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="31" t="str">
+        <v>1099215.5583067</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="32" t="str">
         <f aca="false">IF(E12="","",E12/D12-1)</f>
         <v/>
       </c>
-      <c r="G12" s="32" t="str">
+      <c r="G12" s="33" t="str">
         <f aca="false">IF(E12="","—",IF(ABS(F12)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="D13" s="33" t="n">
+      <c r="A13" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="D13" s="34" t="n">
         <f aca="false">s2_ktor</f>
-        <v>27581.0920251274</v>
-      </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="31" t="str">
+        <v>1709996.21760696</v>
+      </c>
+      <c r="E13" s="35"/>
+      <c r="F13" s="32" t="str">
         <f aca="false">IF(E13="","",E13/D13-1)</f>
         <v/>
       </c>
-      <c r="G13" s="32" t="str">
+      <c r="G13" s="33" t="str">
         <f aca="false">IF(E13="","—",IF(ABS(F13)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="B14" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>322</v>
-      </c>
-      <c r="D14" s="29" t="n">
+      <c r="A14" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="D14" s="30" t="n">
         <f aca="false">s2_flat</f>
-        <v>83.2941853559316</v>
-      </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31" t="str">
+        <v>16.453991975958</v>
+      </c>
+      <c r="E14" s="31"/>
+      <c r="F14" s="32" t="str">
         <f aca="false">IF(E14="","",E14/D14-1)</f>
         <v/>
       </c>
-      <c r="G14" s="32" t="str">
+      <c r="G14" s="33" t="str">
         <f aca="false">IF(E14="","—",IF(ABS(F14)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="D15" s="29" t="n">
+      <c r="A15" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>359</v>
+      </c>
+      <c r="D15" s="30" t="n">
         <f aca="false">s2_fax</f>
-        <v>762.471263539485</v>
-      </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31" t="str">
+        <v>145.76796085664</v>
+      </c>
+      <c r="E15" s="31"/>
+      <c r="F15" s="32" t="str">
         <f aca="false">IF(E15="","",E15/D15-1)</f>
         <v/>
       </c>
-      <c r="G15" s="32" t="str">
+      <c r="G15" s="33" t="str">
         <f aca="false">IF(E15="","—",IF(ABS(F15)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
-        <v>325</v>
-      </c>
-      <c r="B16" s="36" t="s">
-        <v>326</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>324</v>
-      </c>
-      <c r="D16" s="37" t="n">
+      <c r="A16" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>362</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="D16" s="38" t="n">
         <f aca="false">s2_ftor</f>
-        <v>164.081088436435</v>
-      </c>
-      <c r="E16" s="38"/>
-      <c r="F16" s="39" t="str">
+        <v>32.2845970331995</v>
+      </c>
+      <c r="E16" s="39"/>
+      <c r="F16" s="40" t="str">
         <f aca="false">IF(E16="","",E16/D16-1)</f>
         <v/>
       </c>
-      <c r="G16" s="36" t="str">
+      <c r="G16" s="37" t="str">
         <f aca="false">IF(E16="","—",IF(ABS(F16)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="32" t="s">
-        <v>328</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="D17" s="33" t="n">
+      <c r="A17" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D17" s="34" t="n">
         <f aca="false">s3_klat</f>
-        <v>2585.04894108195</v>
-      </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="31" t="str">
+        <v>11602.8270173366</v>
+      </c>
+      <c r="E17" s="35"/>
+      <c r="F17" s="32" t="str">
         <f aca="false">IF(E17="","",E17/D17-1)</f>
         <v/>
       </c>
-      <c r="G17" s="32" t="str">
+      <c r="G17" s="33" t="str">
         <f aca="false">IF(E17="","—",IF(ABS(F17)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H17" s="32"/>
-      <c r="I17" s="35" t="s">
-        <v>330</v>
+      <c r="H17" s="33"/>
+      <c r="I17" s="36" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="32" t="s">
-        <v>328</v>
-      </c>
-      <c r="B18" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="D18" s="33" t="n">
+      <c r="A18" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="D18" s="34" t="n">
         <f aca="false">s3_kax</f>
-        <v>75030.6798078002</v>
-      </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="31" t="str">
+        <v>447456.98582851</v>
+      </c>
+      <c r="E18" s="35"/>
+      <c r="F18" s="32" t="str">
         <f aca="false">IF(E18="","",E18/D18-1)</f>
         <v/>
       </c>
-      <c r="G18" s="32" t="str">
+      <c r="G18" s="33" t="str">
         <f aca="false">IF(E18="","—",IF(ABS(F18)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="32" t="s">
-        <v>328</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="D19" s="33" t="n">
+      <c r="A19" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="D19" s="34" t="n">
         <f aca="false">s3_ktor</f>
-        <v>27510.0227187057</v>
-      </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="31" t="str">
+        <v>1703353.96533777</v>
+      </c>
+      <c r="E19" s="35"/>
+      <c r="F19" s="32" t="str">
         <f aca="false">IF(E19="","",E19/D19-1)</f>
         <v/>
       </c>
-      <c r="G19" s="32" t="str">
+      <c r="G19" s="33" t="str">
         <f aca="false">IF(E19="","—",IF(ABS(F19)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32" t="s">
-        <v>328</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>322</v>
-      </c>
-      <c r="D20" s="29" t="n">
+      <c r="A20" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="D20" s="30" t="n">
         <f aca="false">s3_flat</f>
-        <v>70.3456026207545</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31" t="str">
+        <v>14.5017165499889</v>
+      </c>
+      <c r="E20" s="31"/>
+      <c r="F20" s="32" t="str">
         <f aca="false">IF(E20="","",E20/D20-1)</f>
         <v/>
       </c>
-      <c r="G20" s="32" t="str">
+      <c r="G20" s="33" t="str">
         <f aca="false">IF(E20="","—",IF(ABS(F20)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="32" t="s">
-        <v>328</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="D21" s="29" t="n">
+      <c r="A21" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>359</v>
+      </c>
+      <c r="D21" s="30" t="n">
         <f aca="false">s3_fax</f>
-        <v>377.323845867506</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31" t="str">
+        <v>93.0028573102841</v>
+      </c>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32" t="str">
         <f aca="false">IF(E21="","",E21/D21-1)</f>
         <v/>
       </c>
-      <c r="G21" s="32" t="str">
+      <c r="G21" s="33" t="str">
         <f aca="false">IF(E21="","—",IF(ABS(F21)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
-        <v>328</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>324</v>
-      </c>
-      <c r="D22" s="37" t="n">
+      <c r="A22" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>365</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="D22" s="38" t="n">
         <f aca="false">s3_ftor</f>
-        <v>163.869554919922</v>
-      </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39" t="str">
+        <v>32.2218334187576</v>
+      </c>
+      <c r="E22" s="39"/>
+      <c r="F22" s="40" t="str">
         <f aca="false">IF(E22="","",E22/D22-1)</f>
         <v/>
       </c>
-      <c r="G22" s="36" t="str">
+      <c r="G22" s="37" t="str">
         <f aca="false">IF(E22="","—",IF(ABS(F22)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="B23" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="31" t="str">
+      <c r="A23" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>369</v>
+      </c>
+      <c r="E23" s="35"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="32" t="str">
         <f aca="false">IF(OR(E23="",E17=""),"",E23/E17-1)</f>
         <v/>
       </c>
-      <c r="I23" s="35" t="s">
-        <v>334</v>
+      <c r="I23" s="36" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="B24" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="E24" s="34"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="31" t="str">
+      <c r="A24" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>369</v>
+      </c>
+      <c r="E24" s="35"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="32" t="str">
         <f aca="false">IF(OR(E24="",E18=""),"",E24/E18-1)</f>
         <v/>
       </c>
-      <c r="I24" s="32"/>
+      <c r="I24" s="33"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="D25" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="31" t="str">
+      <c r="A25" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>369</v>
+      </c>
+      <c r="E25" s="35"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="32" t="str">
         <f aca="false">IF(OR(E25="",E19=""),"",E25/E19-1)</f>
         <v/>
       </c>
-      <c r="I25" s="32"/>
+      <c r="I25" s="33"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="B26" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>322</v>
-      </c>
-      <c r="D26" s="41" t="s">
-        <v>333</v>
-      </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="31" t="str">
+      <c r="A26" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="32" t="str">
         <f aca="false">IF(OR(E26="",E20=""),"",E26/E20-1)</f>
         <v/>
       </c>
-      <c r="I26" s="32"/>
+      <c r="I26" s="33"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="D27" s="41" t="s">
-        <v>333</v>
-      </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="31" t="str">
+      <c r="A27" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>359</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="32" t="str">
         <f aca="false">IF(OR(E27="",E21=""),"",E27/E21-1)</f>
         <v/>
       </c>
-      <c r="I27" s="32"/>
+      <c r="I27" s="33"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="36" t="s">
-        <v>331</v>
-      </c>
-      <c r="B28" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>324</v>
-      </c>
-      <c r="D28" s="42" t="s">
-        <v>333</v>
-      </c>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="39" t="str">
+      <c r="A28" s="37" t="s">
+        <v>367</v>
+      </c>
+      <c r="B28" s="37" t="s">
+        <v>368</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>369</v>
+      </c>
+      <c r="E28" s="39"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="40" t="str">
         <f aca="false">IF(OR(E28="",E22=""),"",E28/E22-1)</f>
         <v/>
       </c>
-      <c r="I28" s="36"/>
+      <c r="I28" s="37"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32" t="s">
-        <v>335</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>336</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="D29" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="E29" s="34"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="31" t="str">
+      <c r="A29" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D29" s="41" t="s">
+        <v>369</v>
+      </c>
+      <c r="E29" s="35"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="32" t="str">
         <f aca="false">IF(OR(E29="",E17=""),"",E29/E17-1)</f>
         <v/>
       </c>
-      <c r="I29" s="35" t="s">
-        <v>337</v>
+      <c r="I29" s="36" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
-        <v>335</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>336</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="D30" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="31" t="str">
+      <c r="A30" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="D30" s="41" t="s">
+        <v>369</v>
+      </c>
+      <c r="E30" s="35"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="32" t="str">
         <f aca="false">IF(OR(E30="",E18=""),"",E30/E18-1)</f>
         <v/>
       </c>
-      <c r="I30" s="32"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32" t="s">
-        <v>335</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>336</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="D31" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="E31" s="34"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="31" t="str">
+      <c r="A31" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="D31" s="41" t="s">
+        <v>369</v>
+      </c>
+      <c r="E31" s="35"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="32" t="str">
         <f aca="false">IF(OR(E31="",E19=""),"",E31/E19-1)</f>
         <v/>
       </c>
-      <c r="I31" s="32"/>
+      <c r="I31" s="33"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32" t="s">
-        <v>335</v>
-      </c>
-      <c r="B32" s="32" t="s">
-        <v>336</v>
-      </c>
-      <c r="C32" s="32" t="s">
-        <v>322</v>
-      </c>
-      <c r="D32" s="41" t="s">
-        <v>333</v>
-      </c>
-      <c r="E32" s="30"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="31" t="str">
+      <c r="A32" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="E32" s="31"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="32" t="str">
         <f aca="false">IF(OR(E32="",E20=""),"",E32/E20-1)</f>
         <v/>
       </c>
-      <c r="I32" s="32"/>
+      <c r="I32" s="33"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="32" t="s">
-        <v>335</v>
-      </c>
-      <c r="B33" s="32" t="s">
-        <v>336</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="D33" s="41" t="s">
-        <v>333</v>
-      </c>
-      <c r="E33" s="30"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="31" t="str">
+      <c r="A33" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>359</v>
+      </c>
+      <c r="D33" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="E33" s="31"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="32" t="str">
         <f aca="false">IF(OR(E33="",E21=""),"",E33/E21-1)</f>
         <v/>
       </c>
-      <c r="I33" s="32"/>
+      <c r="I33" s="33"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="36" t="s">
-        <v>335</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>324</v>
-      </c>
-      <c r="D34" s="42" t="s">
-        <v>333</v>
-      </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="39" t="str">
+      <c r="A34" s="37" t="s">
+        <v>371</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>369</v>
+      </c>
+      <c r="E34" s="39"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="40" t="str">
         <f aca="false">IF(OR(E34="",E22=""),"",E34/E22-1)</f>
         <v/>
       </c>
-      <c r="I34" s="36"/>
+      <c r="I34" s="37"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="32" t="s">
-        <v>338</v>
-      </c>
-      <c r="B35" s="32" t="s">
-        <v>339</v>
-      </c>
-      <c r="C35" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="D35" s="33" t="n">
+      <c r="A35" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>375</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D35" s="34" t="n">
         <f aca="false">s4_klat</f>
-        <v>4059.82852217803</v>
-      </c>
-      <c r="E35" s="34"/>
-      <c r="F35" s="31" t="str">
+        <v>15337.4803893591</v>
+      </c>
+      <c r="E35" s="35"/>
+      <c r="F35" s="32" t="str">
         <f aca="false">IF(E35="","",E35/D35-1)</f>
         <v/>
       </c>
-      <c r="G35" s="32" t="str">
+      <c r="G35" s="33" t="str">
         <f aca="false">IF(E35="","—",IF(ABS(F35)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H35" s="32"/>
-      <c r="I35" s="35" t="s">
-        <v>340</v>
+      <c r="H35" s="33"/>
+      <c r="I35" s="36" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="36" t="s">
-        <v>338</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>339</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>322</v>
-      </c>
-      <c r="D36" s="37" t="n">
+      <c r="A36" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="B36" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>358</v>
+      </c>
+      <c r="D36" s="38" t="n">
         <f aca="false">s4_flat</f>
-        <v>88.1569212584955</v>
-      </c>
-      <c r="E36" s="38"/>
-      <c r="F36" s="39" t="str">
+        <v>16.6549044966351</v>
+      </c>
+      <c r="E36" s="39"/>
+      <c r="F36" s="40" t="str">
         <f aca="false">IF(E36="","",E36/D36-1)</f>
         <v/>
       </c>
-      <c r="G36" s="36" t="str">
+      <c r="G36" s="37" t="str">
         <f aca="false">IF(E36="","—",IF(ABS(F36)&lt;=in_tol,"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G5:G37">
